--- a/Docs/Lab03/Lab03_WBT_TCs_Form.xlsx
+++ b/Docs/Lab03/Lab03_WBT_TCs_Form.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15F2A5FB-A6EB-4203-9225-1F69EA3F8E4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CCDDECC-D725-458A-A157-DA7FCE92B656}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Statement" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="121">
   <si>
     <t>Informaţiile vor fi preluate din fişiere text.</t>
   </si>
@@ -38,9 +38,6 @@
     <t>actual result</t>
   </si>
   <si>
-    <t>..</t>
-  </si>
-  <si>
     <t>Final        TC No.</t>
   </si>
   <si>
@@ -126,9 +123,6 @@
   </si>
   <si>
     <t xml:space="preserve">Lab03. White-box Testing. Code Coverage </t>
-  </si>
-  <si>
-    <t>1, 2,4, 6, 7</t>
   </si>
   <si>
     <t>#TCs run</t>
@@ -182,27 +176,6 @@
     <t>F02</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">F02. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>cautarea filmelor care au un anumit regizor (sau parti din numele regizorului).</t>
-    </r>
-  </si>
-  <si>
     <t>F02. Control Flow Graph (CFG)</t>
   </si>
   <si>
@@ -218,28 +191,10 @@
     <t>F02_TC02</t>
   </si>
   <si>
-    <t>F02_Cond01 &gt; 100</t>
-  </si>
-  <si>
-    <t>F02_Cond02 &lt; 20</t>
-  </si>
-  <si>
-    <t>F02_Cond03 == i</t>
-  </si>
-  <si>
-    <t>F02_Condnn &lt; n</t>
-  </si>
-  <si>
     <t>F02_P01</t>
   </si>
   <si>
     <t>F02_P02</t>
-  </si>
-  <si>
-    <t>F02_Pnn</t>
-  </si>
-  <si>
-    <t>F01_TC02</t>
   </si>
   <si>
     <t>F02_P03</t>
@@ -478,24 +433,137 @@
   <si>
     <t>F02_P05</t>
   </si>
+  <si>
+    <t>searchItem</t>
+  </si>
+  <si>
+    <t>Product / NULL</t>
+  </si>
+  <si>
+    <t>Keyboard</t>
+  </si>
+  <si>
+    <t>Product with name "Keyboard"</t>
+  </si>
+  <si>
+    <t>p.getName().contains(searchItem)</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>0, 1, 2, 3, 4, 17</t>
+  </si>
+  <si>
+    <t>Key</t>
+  </si>
+  <si>
+    <t>0, 1, 2, 3, 6, 7, 17</t>
+  </si>
+  <si>
+    <t>(p.getProductId() + "").equals(searchItem)</t>
+  </si>
+  <si>
+    <t>XYZ</t>
+  </si>
+  <si>
+    <t>F02_TC03</t>
+  </si>
+  <si>
+    <t>F02_TC04</t>
+  </si>
+  <si>
+    <t>NULL</t>
+  </si>
+  <si>
+    <t>0, 1, 2, 3, 5, 6, 10, 12, 16, 17</t>
+  </si>
+  <si>
+    <t>isFound == false</t>
+  </si>
+  <si>
+    <t>for (Product p : products)</t>
+  </si>
+  <si>
+    <t>""</t>
+  </si>
+  <si>
+    <t>F02_TC05</t>
+  </si>
+  <si>
+    <t>FO2_TCO6</t>
+  </si>
+  <si>
+    <t>Keyboard (Empty products list)</t>
+  </si>
+  <si>
+    <t>Empty Product</t>
+  </si>
+  <si>
+    <t>0, 1, 2, 12, 13, 14, 17</t>
+  </si>
+  <si>
+    <t>FO2_TCO7</t>
+  </si>
+  <si>
+    <t>Thrown error</t>
+  </si>
+  <si>
+    <t>0, 1, 2, 3, 17</t>
+  </si>
+  <si>
+    <t>Product with id 102</t>
+  </si>
+  <si>
+    <t>F02_TC06</t>
+  </si>
+  <si>
+    <t>F02_TC07</t>
+  </si>
+  <si>
+    <t>Products</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(id, name, price, inStock, min, max, parts)
+(101, "Keyboard", 29.99, 15, 5, 20, []);
+(102, "Monitor", 199.99, 8, 2, 10, []);
+</t>
+  </si>
+  <si>
+    <t>Repository EMPTY ()</t>
+  </si>
+  <si>
+    <t>(101, "Keyboard", 29.99, 15, 5, 20, [])</t>
+  </si>
+  <si>
+    <t>(102, "Monitor", 199.99, 8, 2, 10, [])</t>
+  </si>
+  <si>
+    <t>(0,"",0,0,0,[])</t>
+  </si>
+  <si>
+    <t>exception</t>
+  </si>
+  <si>
+    <t>Application tries to read name of a NULL object. 
+Application returns an empty product instead of null when repository is empty.
+2 Bugs.</t>
+  </si>
+  <si>
+    <t>da</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -581,28 +649,6 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <i/>
       <sz val="9"/>
       <color rgb="FFFF0000"/>
@@ -619,7 +665,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -700,7 +754,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="33">
+  <borders count="39">
     <border>
       <left/>
       <right/>
@@ -1081,14 +1135,16 @@
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
         <color indexed="64"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color indexed="64"/>
       </right>
       <top/>
@@ -1098,14 +1154,80 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color indexed="64"/>
       </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="double">
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1114,45 +1236,203 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1161,7 +1441,16 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1169,215 +1458,49 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="9" fontId="0" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1401,15 +1524,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>352838</xdr:colOff>
+      <xdr:colOff>451450</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>17930</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>29</xdr:col>
-      <xdr:colOff>2269</xdr:colOff>
+      <xdr:colOff>100881</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>147790</xdr:rowOff>
+      <xdr:rowOff>165720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1439,7 +1562,7 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="8967920" y="0"/>
+          <a:off x="9066532" y="17930"/>
           <a:ext cx="8918937" cy="4271555"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1810,48 +1933,48 @@
   <sheetData>
     <row r="1" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B1" s="12"/>
-      <c r="D1" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="40"/>
+      <c r="D1" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="29"/>
     </row>
     <row r="2" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B2" s="37" t="s">
-        <v>65</v>
+      <c r="B2" s="24" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O4" s="5"/>
       <c r="P4" s="5"/>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="N5" s="35" t="s">
-        <v>58</v>
-      </c>
-      <c r="O5" s="35"/>
-      <c r="P5" s="35"/>
+        <v>29</v>
+      </c>
+      <c r="N5" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="O5" s="22"/>
+      <c r="P5" s="22"/>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="N6" s="29"/>
-      <c r="O6" s="29" t="s">
-        <v>63</v>
-      </c>
-      <c r="P6" s="29" t="s">
-        <v>59</v>
+      <c r="N6" s="17"/>
+      <c r="O6" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="P6" s="17" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.3">
@@ -1859,13 +1982,13 @@
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
-      <c r="N7" s="29" t="s">
-        <v>60</v>
-      </c>
-      <c r="O7" s="29" t="s">
-        <v>79</v>
-      </c>
-      <c r="P7" s="29">
+      <c r="N7" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="O7" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="P7" s="17">
         <v>232</v>
       </c>
     </row>
@@ -1874,44 +1997,44 @@
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
-      <c r="N8" s="29" t="s">
-        <v>61</v>
-      </c>
-      <c r="O8" s="29" t="s">
-        <v>80</v>
-      </c>
-      <c r="P8" s="29">
+      <c r="N8" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="O8" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="P8" s="17">
         <v>232</v>
       </c>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
-      <c r="N9" s="29" t="s">
-        <v>62</v>
-      </c>
-      <c r="O9" s="29" t="s">
-        <v>81</v>
-      </c>
-      <c r="P9" s="29">
+      <c r="N9" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="O9" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="P9" s="17">
         <v>232</v>
       </c>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B11" s="95" t="s">
-        <v>82</v>
+      <c r="B11" s="25" t="s">
+        <v>73</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
@@ -1951,327 +2074,335 @@
   <sheetData>
     <row r="1" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B1" s="12"/>
-      <c r="D1" s="38" t="s">
+      <c r="D1" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="29"/>
+    </row>
+    <row r="3" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B3" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
+      <c r="K3" s="35"/>
+    </row>
+    <row r="6" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B6" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="28"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="28"/>
+      <c r="Q6" s="27"/>
+      <c r="R6" s="28"/>
+      <c r="S6" s="28"/>
+      <c r="T6" s="28"/>
+    </row>
+    <row r="8" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B8" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="21">
+        <v>5</v>
+      </c>
+      <c r="I8" s="12"/>
+      <c r="Q8" s="31"/>
+      <c r="R8" s="31"/>
+      <c r="S8" s="31"/>
+      <c r="T8" s="21"/>
+    </row>
+    <row r="9" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B9" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="I9" s="23"/>
+      <c r="Q9" s="31"/>
+      <c r="R9" s="31"/>
+      <c r="S9" s="31"/>
+      <c r="T9" s="21"/>
+    </row>
+    <row r="10" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B10" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="31" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="31"/>
+      <c r="E10" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="I10" s="26"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="26"/>
+      <c r="M10" s="26"/>
+      <c r="N10" s="26"/>
+      <c r="O10" s="26"/>
+      <c r="Q10" s="31"/>
+      <c r="R10" s="31"/>
+      <c r="S10" s="31"/>
+      <c r="T10" s="21"/>
+    </row>
+    <row r="11" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="I11" s="26"/>
+      <c r="J11" s="26"/>
+      <c r="K11" s="26"/>
+      <c r="L11" s="26"/>
+      <c r="M11" s="26"/>
+      <c r="N11" s="26"/>
+      <c r="O11" s="26"/>
+    </row>
+    <row r="12" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="I12" s="26"/>
+      <c r="J12" s="26"/>
+      <c r="K12" s="26"/>
+      <c r="L12" s="26"/>
+      <c r="M12" s="26"/>
+      <c r="N12" s="26"/>
+      <c r="O12" s="26"/>
+    </row>
+    <row r="13" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B13" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="I13" s="26"/>
+      <c r="J13" s="26"/>
+      <c r="K13" s="26"/>
+      <c r="L13" s="26"/>
+      <c r="M13" s="26"/>
+      <c r="N13" s="26"/>
+      <c r="O13" s="26"/>
+      <c r="Q13" s="27"/>
+      <c r="R13" s="28"/>
+      <c r="S13" s="28"/>
+      <c r="T13" s="28"/>
+    </row>
+    <row r="14" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="I14" s="26"/>
+      <c r="J14" s="26"/>
+      <c r="K14" s="26"/>
+      <c r="L14" s="26"/>
+      <c r="M14" s="26"/>
+      <c r="N14" s="26"/>
+      <c r="O14" s="26"/>
+    </row>
+    <row r="15" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B15" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="I15" s="26"/>
+      <c r="J15" s="26"/>
+      <c r="K15" s="26"/>
+      <c r="L15" s="26"/>
+      <c r="M15" s="26"/>
+      <c r="N15" s="26"/>
+      <c r="O15" s="26"/>
+      <c r="Q15" s="20"/>
+      <c r="R15" s="32"/>
+      <c r="S15" s="32"/>
+      <c r="T15" s="32"/>
+    </row>
+    <row r="16" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B16" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
+      <c r="I16" s="26"/>
+      <c r="J16" s="26"/>
+      <c r="K16" s="26"/>
+      <c r="L16" s="26"/>
+      <c r="M16" s="26"/>
+      <c r="N16" s="26"/>
+      <c r="O16" s="26"/>
+      <c r="Q16" s="22"/>
+      <c r="R16" s="30"/>
+      <c r="S16" s="30"/>
+      <c r="T16" s="30"/>
+    </row>
+    <row r="17" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B17" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="D17" s="30"/>
+      <c r="E17" s="30"/>
+      <c r="I17" s="26"/>
+      <c r="J17" s="26"/>
+      <c r="K17" s="26"/>
+      <c r="L17" s="26"/>
+      <c r="M17" s="26"/>
+      <c r="N17" s="26"/>
+      <c r="O17" s="26"/>
+      <c r="Q17" s="22"/>
+      <c r="R17" s="30"/>
+      <c r="S17" s="30"/>
+      <c r="T17" s="30"/>
+    </row>
+    <row r="18" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B18" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="40"/>
-    </row>
-    <row r="3" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B3" s="96" t="s">
+      <c r="D18" s="30"/>
+      <c r="E18" s="30"/>
+      <c r="I18" s="26"/>
+      <c r="J18" s="26"/>
+      <c r="K18" s="26"/>
+      <c r="L18" s="26"/>
+      <c r="M18" s="26"/>
+      <c r="N18" s="26"/>
+      <c r="O18" s="26"/>
+      <c r="Q18" s="22"/>
+      <c r="R18" s="30"/>
+      <c r="S18" s="30"/>
+      <c r="T18" s="30"/>
+    </row>
+    <row r="19" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B19" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="C19" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="D19" s="30"/>
+      <c r="E19" s="30"/>
+      <c r="I19" s="26"/>
+      <c r="J19" s="26"/>
+      <c r="K19" s="26"/>
+      <c r="L19" s="26"/>
+      <c r="M19" s="26"/>
+      <c r="N19" s="26"/>
+      <c r="O19" s="26"/>
+      <c r="Q19" s="22"/>
+      <c r="R19" s="30"/>
+      <c r="S19" s="30"/>
+      <c r="T19" s="30"/>
+    </row>
+    <row r="20" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B20" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
-      <c r="K3" s="45"/>
-    </row>
-    <row r="6" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B6" s="38" t="s">
-        <v>44</v>
-      </c>
-      <c r="C6" s="39"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="Q6" s="38"/>
-      <c r="R6" s="39"/>
-      <c r="S6" s="39"/>
-      <c r="T6" s="39"/>
-    </row>
-    <row r="8" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B8" s="42" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="42"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="34">
-        <v>5</v>
-      </c>
-      <c r="I8" s="12"/>
-      <c r="Q8" s="42"/>
-      <c r="R8" s="42"/>
-      <c r="S8" s="42"/>
-      <c r="T8" s="34"/>
-    </row>
-    <row r="9" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B9" s="42" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="42"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="99" t="s">
-        <v>83</v>
-      </c>
-      <c r="I9" s="36"/>
-      <c r="Q9" s="42"/>
-      <c r="R9" s="42"/>
-      <c r="S9" s="42"/>
-      <c r="T9" s="34"/>
-    </row>
-    <row r="10" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B10" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="42" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" s="42"/>
-      <c r="E10" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="I10" s="97"/>
-      <c r="J10" s="97"/>
-      <c r="K10" s="97"/>
-      <c r="L10" s="97"/>
-      <c r="M10" s="97"/>
-      <c r="N10" s="97"/>
-      <c r="O10" s="97"/>
-      <c r="Q10" s="42"/>
-      <c r="R10" s="42"/>
-      <c r="S10" s="42"/>
-      <c r="T10" s="34"/>
-    </row>
-    <row r="11" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="I11" s="97"/>
-      <c r="J11" s="97"/>
-      <c r="K11" s="97"/>
-      <c r="L11" s="97"/>
-      <c r="M11" s="97"/>
-      <c r="N11" s="97"/>
-      <c r="O11" s="97"/>
-    </row>
-    <row r="12" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="I12" s="97"/>
-      <c r="J12" s="97"/>
-      <c r="K12" s="97"/>
-      <c r="L12" s="97"/>
-      <c r="M12" s="97"/>
-      <c r="N12" s="97"/>
-      <c r="O12" s="97"/>
-    </row>
-    <row r="13" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B13" s="38" t="s">
-        <v>45</v>
-      </c>
-      <c r="C13" s="39"/>
-      <c r="D13" s="39"/>
-      <c r="E13" s="39"/>
-      <c r="I13" s="97"/>
-      <c r="J13" s="97"/>
-      <c r="K13" s="97"/>
-      <c r="L13" s="97"/>
-      <c r="M13" s="97"/>
-      <c r="N13" s="97"/>
-      <c r="O13" s="97"/>
-      <c r="Q13" s="38"/>
-      <c r="R13" s="39"/>
-      <c r="S13" s="39"/>
-      <c r="T13" s="39"/>
-    </row>
-    <row r="14" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="I14" s="97"/>
-      <c r="J14" s="97"/>
-      <c r="K14" s="97"/>
-      <c r="L14" s="97"/>
-      <c r="M14" s="97"/>
-      <c r="N14" s="97"/>
-      <c r="O14" s="97"/>
-    </row>
-    <row r="15" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B15" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="C15" s="46" t="s">
-        <v>14</v>
-      </c>
-      <c r="D15" s="46"/>
-      <c r="E15" s="46"/>
-      <c r="I15" s="97"/>
-      <c r="J15" s="97"/>
-      <c r="K15" s="97"/>
-      <c r="L15" s="97"/>
-      <c r="M15" s="97"/>
-      <c r="N15" s="97"/>
-      <c r="O15" s="97"/>
-      <c r="Q15" s="33"/>
-      <c r="R15" s="46"/>
-      <c r="S15" s="46"/>
-      <c r="T15" s="46"/>
-    </row>
-    <row r="16" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B16" s="35" t="s">
-        <v>52</v>
-      </c>
-      <c r="C16" s="41" t="s">
-        <v>85</v>
-      </c>
-      <c r="D16" s="41"/>
-      <c r="E16" s="41"/>
-      <c r="I16" s="97"/>
-      <c r="J16" s="97"/>
-      <c r="K16" s="97"/>
-      <c r="L16" s="97"/>
-      <c r="M16" s="97"/>
-      <c r="N16" s="97"/>
-      <c r="O16" s="97"/>
-      <c r="Q16" s="35"/>
-      <c r="R16" s="41"/>
-      <c r="S16" s="41"/>
-      <c r="T16" s="41"/>
-    </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B17" s="35" t="s">
-        <v>53</v>
-      </c>
-      <c r="C17" s="41" t="s">
-        <v>86</v>
-      </c>
-      <c r="D17" s="41"/>
-      <c r="E17" s="41"/>
-      <c r="I17" s="97"/>
-      <c r="J17" s="97"/>
-      <c r="K17" s="97"/>
-      <c r="L17" s="97"/>
-      <c r="M17" s="97"/>
-      <c r="N17" s="97"/>
-      <c r="O17" s="97"/>
-      <c r="Q17" s="35"/>
-      <c r="R17" s="41"/>
-      <c r="S17" s="41"/>
-      <c r="T17" s="41"/>
-    </row>
-    <row r="18" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B18" s="35" t="s">
-        <v>56</v>
-      </c>
-      <c r="C18" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="D18" s="41"/>
-      <c r="E18" s="41"/>
-      <c r="I18" s="97"/>
-      <c r="J18" s="97"/>
-      <c r="K18" s="97"/>
-      <c r="L18" s="97"/>
-      <c r="M18" s="97"/>
-      <c r="N18" s="97"/>
-      <c r="O18" s="97"/>
-      <c r="Q18" s="35"/>
-      <c r="R18" s="41"/>
-      <c r="S18" s="41"/>
-      <c r="T18" s="41"/>
-    </row>
-    <row r="19" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B19" s="35" t="s">
-        <v>89</v>
-      </c>
-      <c r="C19" s="41" t="s">
-        <v>88</v>
-      </c>
-      <c r="D19" s="41"/>
-      <c r="E19" s="41"/>
-      <c r="I19" s="97"/>
-      <c r="J19" s="97"/>
-      <c r="K19" s="97"/>
-      <c r="L19" s="97"/>
-      <c r="M19" s="97"/>
-      <c r="N19" s="97"/>
-      <c r="O19" s="97"/>
-      <c r="Q19" s="35"/>
-      <c r="R19" s="41"/>
-      <c r="S19" s="41"/>
-      <c r="T19" s="41"/>
-    </row>
-    <row r="20" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B20" s="35" t="s">
-        <v>91</v>
-      </c>
-      <c r="C20" s="41" t="s">
-        <v>90</v>
-      </c>
-      <c r="D20" s="41"/>
-      <c r="E20" s="41"/>
-      <c r="I20" s="97"/>
-      <c r="J20" s="97"/>
-      <c r="K20" s="97"/>
-      <c r="L20" s="97"/>
-      <c r="M20" s="97"/>
-      <c r="N20" s="97"/>
-      <c r="O20" s="97"/>
-      <c r="Q20" s="35"/>
-      <c r="R20" s="41"/>
-      <c r="S20" s="41"/>
-      <c r="T20" s="41"/>
+      <c r="C20" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="I20" s="26"/>
+      <c r="J20" s="26"/>
+      <c r="K20" s="26"/>
+      <c r="L20" s="26"/>
+      <c r="M20" s="26"/>
+      <c r="N20" s="26"/>
+      <c r="O20" s="26"/>
+      <c r="Q20" s="22"/>
+      <c r="R20" s="30"/>
+      <c r="S20" s="30"/>
+      <c r="T20" s="30"/>
     </row>
     <row r="21" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B21" s="35" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="41" t="s">
+      <c r="B21" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="D21" s="41"/>
-      <c r="E21" s="41"/>
-      <c r="I21" s="98"/>
-      <c r="J21" s="98"/>
-      <c r="K21" s="98"/>
-      <c r="L21" s="98"/>
-      <c r="M21" s="97"/>
-      <c r="N21" s="97"/>
-      <c r="O21" s="97"/>
-      <c r="Q21" s="35"/>
-      <c r="R21" s="41"/>
-      <c r="S21" s="41"/>
-      <c r="T21" s="41"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="30"/>
+      <c r="M21" s="26"/>
+      <c r="N21" s="26"/>
+      <c r="O21" s="26"/>
+      <c r="Q21" s="22"/>
+      <c r="R21" s="30"/>
+      <c r="S21" s="30"/>
+      <c r="T21" s="30"/>
     </row>
     <row r="22" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="I22" s="98"/>
-      <c r="J22" s="98"/>
-      <c r="K22" s="98"/>
-      <c r="L22" s="98"/>
-      <c r="M22" s="97"/>
-      <c r="N22" s="97"/>
-      <c r="O22" s="97"/>
+      <c r="M22" s="26"/>
+      <c r="N22" s="26"/>
+      <c r="O22" s="26"/>
     </row>
     <row r="23" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="I23" s="97"/>
-      <c r="J23" s="97"/>
-      <c r="K23" s="97"/>
-      <c r="L23" s="97"/>
-      <c r="M23" s="97"/>
-      <c r="N23" s="97"/>
-      <c r="O23" s="97"/>
+      <c r="I23" s="26"/>
+      <c r="J23" s="26"/>
+      <c r="K23" s="26"/>
+      <c r="L23" s="26"/>
+      <c r="M23" s="26"/>
+      <c r="N23" s="26"/>
+      <c r="O23" s="26"/>
     </row>
     <row r="24" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="I24" s="97"/>
-      <c r="J24" s="97"/>
-      <c r="K24" s="97"/>
-      <c r="L24" s="97"/>
-      <c r="M24" s="97"/>
-      <c r="N24" s="97"/>
-      <c r="O24" s="97"/>
+      <c r="I24" s="26"/>
+      <c r="J24" s="26"/>
+      <c r="K24" s="26"/>
+      <c r="L24" s="26"/>
+      <c r="M24" s="26"/>
+      <c r="N24" s="26"/>
+      <c r="O24" s="26"/>
     </row>
     <row r="61" spans="4:10" x14ac:dyDescent="0.3">
-      <c r="D61" s="38" t="s">
-        <v>43</v>
-      </c>
-      <c r="E61" s="39"/>
-      <c r="F61" s="39"/>
-      <c r="G61" s="39"/>
-      <c r="H61" s="39"/>
-      <c r="I61" s="39"/>
-      <c r="J61" s="39"/>
+      <c r="D61" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="E61" s="28"/>
+      <c r="F61" s="28"/>
+      <c r="G61" s="28"/>
+      <c r="H61" s="28"/>
+      <c r="I61" s="28"/>
+      <c r="J61" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="D61:J61"/>
+    <mergeCell ref="Q6:T6"/>
+    <mergeCell ref="R17:T17"/>
+    <mergeCell ref="R19:T19"/>
+    <mergeCell ref="R18:T18"/>
+    <mergeCell ref="Q9:S9"/>
+    <mergeCell ref="R16:T16"/>
+    <mergeCell ref="Q13:T13"/>
+    <mergeCell ref="D1:I1"/>
+    <mergeCell ref="R20:T20"/>
+    <mergeCell ref="R21:T21"/>
+    <mergeCell ref="B3:K3"/>
+    <mergeCell ref="Q10:S10"/>
+    <mergeCell ref="R15:T15"/>
+    <mergeCell ref="Q8:S8"/>
+    <mergeCell ref="B6:E6"/>
     <mergeCell ref="C21:E21"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B9:D9"/>
@@ -2283,22 +2414,6 @@
     <mergeCell ref="C18:E18"/>
     <mergeCell ref="C19:E19"/>
     <mergeCell ref="C20:E20"/>
-    <mergeCell ref="D1:I1"/>
-    <mergeCell ref="R20:T20"/>
-    <mergeCell ref="R21:T21"/>
-    <mergeCell ref="B3:K3"/>
-    <mergeCell ref="Q10:S10"/>
-    <mergeCell ref="R15:T15"/>
-    <mergeCell ref="Q8:S8"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="D61:J61"/>
-    <mergeCell ref="Q6:T6"/>
-    <mergeCell ref="R17:T17"/>
-    <mergeCell ref="R19:T19"/>
-    <mergeCell ref="R18:T18"/>
-    <mergeCell ref="Q9:S9"/>
-    <mergeCell ref="R16:T16"/>
-    <mergeCell ref="Q13:T13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2311,476 +2426,542 @@
   <sheetPr>
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B1:AB16"/>
+  <dimension ref="B1:Y16"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.21875" customWidth="1"/>
     <col min="3" max="4" width="18.21875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.21875" customWidth="1"/>
-    <col min="7" max="7" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.21875" customWidth="1"/>
-    <col min="9" max="9" width="9.21875" customWidth="1"/>
-    <col min="10" max="10" width="14.6640625" customWidth="1"/>
-    <col min="11" max="11" width="6.109375" customWidth="1"/>
-    <col min="12" max="12" width="6.44140625" customWidth="1"/>
-    <col min="13" max="13" width="5" customWidth="1"/>
-    <col min="15" max="15" width="11.77734375" customWidth="1"/>
-    <col min="16" max="16" width="8.77734375" customWidth="1"/>
-    <col min="17" max="17" width="8.88671875" customWidth="1"/>
-    <col min="21" max="21" width="9.109375" customWidth="1"/>
-    <col min="22" max="22" width="2.21875" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="2.109375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="3.5546875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="2.21875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="4.109375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="5.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="13" width="13.77734375" customWidth="1"/>
+    <col min="14" max="14" width="8.77734375" customWidth="1"/>
+    <col min="15" max="15" width="8.88671875" customWidth="1"/>
+    <col min="19" max="19" width="2.21875" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="2.109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="3.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="2.21875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="4.109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="5.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:28" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B1" s="12"/>
-      <c r="D1" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="40"/>
-    </row>
-    <row r="3" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B3" s="43" t="s">
-        <v>42</v>
-      </c>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="45"/>
-    </row>
-    <row r="5" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="D1" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="29"/>
+    </row>
+    <row r="3" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="B3" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="35"/>
+    </row>
+    <row r="5" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B5" s="11"/>
     </row>
-    <row r="6" spans="2:28" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B6" s="53" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="53" t="s">
+    <row r="6" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B6" s="71" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="71" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="72" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="54" t="s">
+      <c r="E6" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="53" t="s">
+      <c r="F6" s="71"/>
+      <c r="G6" s="71"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="71"/>
+      <c r="K6" s="71"/>
+      <c r="L6" s="71"/>
+      <c r="M6" s="71"/>
+      <c r="N6" s="71"/>
+      <c r="O6" s="71"/>
+      <c r="P6" s="71"/>
+      <c r="Q6" s="71"/>
+      <c r="R6" s="71"/>
+      <c r="S6" s="71"/>
+      <c r="T6" s="71"/>
+      <c r="U6" s="71"/>
+      <c r="V6" s="71"/>
+      <c r="W6" s="71"/>
+      <c r="X6" s="71"/>
+      <c r="Y6" s="71"/>
+    </row>
+    <row r="7" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B7" s="71"/>
+      <c r="C7" s="71"/>
+      <c r="D7" s="73"/>
+      <c r="E7" s="74" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="75" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="75"/>
+      <c r="H7" s="75"/>
+      <c r="I7" s="75"/>
+      <c r="J7" s="75"/>
+      <c r="K7" s="75"/>
+      <c r="L7" s="75"/>
+      <c r="M7" s="75"/>
+      <c r="N7" s="76" t="s">
+        <v>55</v>
+      </c>
+      <c r="O7" s="76"/>
+      <c r="P7" s="76"/>
+      <c r="Q7" s="76"/>
+      <c r="R7" s="76"/>
+      <c r="S7" s="77" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="53"/>
-      <c r="G6" s="53"/>
-      <c r="H6" s="53"/>
-      <c r="I6" s="53"/>
-      <c r="J6" s="53"/>
-      <c r="K6" s="53"/>
-      <c r="L6" s="53"/>
-      <c r="M6" s="53"/>
-      <c r="N6" s="53"/>
-      <c r="O6" s="53"/>
-      <c r="P6" s="53"/>
-      <c r="Q6" s="53"/>
-      <c r="R6" s="53"/>
-      <c r="S6" s="53"/>
-      <c r="T6" s="53"/>
-      <c r="U6" s="53"/>
-      <c r="V6" s="53"/>
-      <c r="W6" s="53"/>
-      <c r="X6" s="53"/>
-      <c r="Y6" s="53"/>
-      <c r="Z6" s="53"/>
-      <c r="AA6" s="53"/>
-      <c r="AB6" s="53"/>
-    </row>
-    <row r="7" spans="2:28" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B7" s="53"/>
-      <c r="C7" s="53"/>
-      <c r="D7" s="55"/>
-      <c r="E7" s="50" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7" s="49" t="s">
-        <v>32</v>
-      </c>
-      <c r="G7" s="49"/>
-      <c r="H7" s="49"/>
-      <c r="I7" s="49"/>
-      <c r="J7" s="49"/>
-      <c r="K7" s="49"/>
-      <c r="L7" s="49"/>
-      <c r="M7" s="49"/>
-      <c r="N7" s="49"/>
-      <c r="O7" s="49"/>
-      <c r="P7" s="51" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q7" s="51"/>
-      <c r="R7" s="51"/>
-      <c r="S7" s="51"/>
-      <c r="T7" s="51"/>
-      <c r="U7" s="51"/>
-      <c r="V7" s="52" t="s">
+      <c r="T7" s="77"/>
+      <c r="U7" s="77"/>
+      <c r="V7" s="77"/>
+      <c r="W7" s="77"/>
+      <c r="X7" s="77"/>
+      <c r="Y7" s="77"/>
+    </row>
+    <row r="8" spans="2:25" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="71"/>
+      <c r="C8" s="78" t="s">
+        <v>83</v>
+      </c>
+      <c r="D8" s="78" t="s">
+        <v>84</v>
+      </c>
+      <c r="E8" s="74"/>
+      <c r="F8" s="75" t="s">
+        <v>87</v>
+      </c>
+      <c r="G8" s="75"/>
+      <c r="H8" s="75" t="s">
+        <v>92</v>
+      </c>
+      <c r="I8" s="75"/>
+      <c r="J8" s="75" t="s">
+        <v>98</v>
+      </c>
+      <c r="K8" s="75"/>
+      <c r="L8" s="75" t="s">
+        <v>99</v>
+      </c>
+      <c r="M8" s="75"/>
+      <c r="N8" s="76" t="s">
+        <v>45</v>
+      </c>
+      <c r="O8" s="76" t="s">
+        <v>46</v>
+      </c>
+      <c r="P8" s="76" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q8" s="76" t="s">
+        <v>80</v>
+      </c>
+      <c r="R8" s="76" t="s">
+        <v>82</v>
+      </c>
+      <c r="S8" s="77">
+        <v>0</v>
+      </c>
+      <c r="T8" s="77">
+        <v>1</v>
+      </c>
+      <c r="U8" s="77">
+        <v>2</v>
+      </c>
+      <c r="V8" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="W7" s="52"/>
-      <c r="X7" s="52"/>
-      <c r="Y7" s="52"/>
-      <c r="Z7" s="52"/>
-      <c r="AA7" s="52"/>
-      <c r="AB7" s="52"/>
-    </row>
-    <row r="8" spans="2:28" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="53"/>
-      <c r="C8" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="E8" s="50"/>
-      <c r="F8" s="49" t="s">
-        <v>48</v>
-      </c>
-      <c r="G8" s="49"/>
-      <c r="H8" s="49" t="s">
-        <v>49</v>
-      </c>
-      <c r="I8" s="49"/>
-      <c r="J8" s="49" t="s">
-        <v>50</v>
-      </c>
-      <c r="K8" s="49"/>
-      <c r="L8" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="M8" s="49"/>
-      <c r="N8" s="49" t="s">
-        <v>51</v>
-      </c>
-      <c r="O8" s="49"/>
-      <c r="P8" s="51" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q8" s="51" t="s">
-        <v>53</v>
-      </c>
-      <c r="R8" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="S8" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="T8" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="U8" s="51" t="s">
-        <v>54</v>
-      </c>
-      <c r="V8" s="52">
-        <v>0</v>
-      </c>
-      <c r="W8" s="52">
-        <v>1</v>
-      </c>
-      <c r="X8" s="52">
-        <v>2</v>
-      </c>
-      <c r="Y8" s="52" t="s">
+      <c r="W8" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="Z8" s="52" t="s">
+      <c r="X8" s="77" t="s">
         <v>20</v>
       </c>
-      <c r="AA8" s="52" t="s">
+      <c r="Y8" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="AB8" s="52" t="s">
+    </row>
+    <row r="9" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B9" s="71"/>
+      <c r="C9" s="79"/>
+      <c r="D9" s="79"/>
+      <c r="E9" s="74"/>
+      <c r="F9" s="80" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="9" spans="2:28" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B9" s="53"/>
-      <c r="C9" s="48"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="50"/>
-      <c r="F9" s="13" t="s">
+      <c r="G9" s="80" t="s">
         <v>23</v>
       </c>
-      <c r="G9" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="H9" s="13" t="s">
+      <c r="H9" s="80" t="s">
+        <v>22</v>
+      </c>
+      <c r="I9" s="80" t="s">
         <v>23</v>
       </c>
-      <c r="I9" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J9" s="13" t="s">
+      <c r="J9" s="80" t="s">
+        <v>22</v>
+      </c>
+      <c r="K9" s="80" t="s">
         <v>23</v>
       </c>
-      <c r="K9" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="L9" s="13" t="s">
+      <c r="L9" s="80" t="s">
+        <v>22</v>
+      </c>
+      <c r="M9" s="80" t="s">
         <v>23</v>
       </c>
-      <c r="M9" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="N9" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="O9" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="P9" s="51"/>
-      <c r="Q9" s="51"/>
-      <c r="R9" s="51"/>
-      <c r="S9" s="51"/>
-      <c r="T9" s="51"/>
-      <c r="U9" s="51"/>
-      <c r="V9" s="52"/>
-      <c r="W9" s="52"/>
-      <c r="X9" s="52"/>
-      <c r="Y9" s="52"/>
-      <c r="Z9" s="52"/>
-      <c r="AA9" s="52"/>
-      <c r="AB9" s="52"/>
-    </row>
-    <row r="10" spans="2:28" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B10" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="E10" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="17"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="17"/>
-      <c r="L10" s="17"/>
-      <c r="M10" s="17"/>
-      <c r="N10" s="17"/>
-      <c r="O10" s="17"/>
-      <c r="P10" s="18"/>
-      <c r="Q10" s="18"/>
-      <c r="R10" s="18"/>
-      <c r="S10" s="18"/>
-      <c r="T10" s="18"/>
-      <c r="U10" s="18"/>
-      <c r="V10" s="19"/>
-      <c r="W10" s="19"/>
-      <c r="X10" s="19"/>
-      <c r="Y10" s="19"/>
-      <c r="Z10" s="19"/>
-      <c r="AA10" s="19"/>
-      <c r="AB10" s="19"/>
-    </row>
-    <row r="11" spans="2:28" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B11" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="E11" s="16"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="17"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="17"/>
-      <c r="L11" s="17"/>
-      <c r="M11" s="17"/>
-      <c r="N11" s="17"/>
-      <c r="O11" s="17"/>
-      <c r="P11" s="18"/>
-      <c r="Q11" s="18"/>
-      <c r="R11" s="18"/>
-      <c r="S11" s="18"/>
-      <c r="T11" s="18"/>
-      <c r="U11" s="18"/>
-      <c r="V11" s="19"/>
-      <c r="W11" s="19"/>
-      <c r="X11" s="19"/>
-      <c r="Y11" s="19"/>
-      <c r="Z11" s="19"/>
-      <c r="AA11" s="19"/>
-      <c r="AB11" s="19"/>
-    </row>
-    <row r="12" spans="2:28" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B12" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="C12" s="20"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="17"/>
-      <c r="J12" s="17"/>
-      <c r="K12" s="17"/>
-      <c r="L12" s="17"/>
-      <c r="M12" s="17"/>
-      <c r="N12" s="17"/>
-      <c r="O12" s="17"/>
-      <c r="P12" s="18"/>
-      <c r="Q12" s="18"/>
-      <c r="R12" s="18"/>
-      <c r="S12" s="18"/>
-      <c r="T12" s="18"/>
-      <c r="U12" s="18"/>
-      <c r="V12" s="19"/>
-      <c r="W12" s="19"/>
-      <c r="X12" s="19"/>
-      <c r="Y12" s="19"/>
-      <c r="Z12" s="19"/>
-      <c r="AA12" s="19"/>
-      <c r="AB12" s="19"/>
-    </row>
-    <row r="13" spans="2:28" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B13" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="C13" s="14"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="17"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="17"/>
-      <c r="L13" s="17"/>
-      <c r="M13" s="17"/>
-      <c r="N13" s="17"/>
-      <c r="O13" s="17"/>
-      <c r="P13" s="18"/>
-      <c r="Q13" s="18"/>
-      <c r="R13" s="18"/>
-      <c r="S13" s="18"/>
-      <c r="T13" s="18"/>
-      <c r="U13" s="18"/>
-      <c r="V13" s="19"/>
-      <c r="W13" s="19"/>
-      <c r="X13" s="19"/>
-      <c r="Y13" s="19"/>
-      <c r="Z13" s="19"/>
-      <c r="AA13" s="19"/>
-      <c r="AB13" s="19"/>
-    </row>
-    <row r="14" spans="2:28" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B14" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="C14" s="14"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="17"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="17"/>
-      <c r="L14" s="17"/>
-      <c r="M14" s="17"/>
-      <c r="N14" s="17"/>
-      <c r="O14" s="17"/>
-      <c r="P14" s="18"/>
-      <c r="Q14" s="18"/>
-      <c r="R14" s="18"/>
-      <c r="S14" s="18"/>
-      <c r="T14" s="18"/>
-      <c r="U14" s="18"/>
-      <c r="V14" s="19"/>
-      <c r="W14" s="19"/>
-      <c r="X14" s="19"/>
-      <c r="Y14" s="19"/>
-      <c r="Z14" s="19"/>
-      <c r="AA14" s="19"/>
-      <c r="AB14" s="19"/>
-    </row>
-    <row r="15" spans="2:28" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B15" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="C15" s="14"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="17"/>
-      <c r="K15" s="17"/>
-      <c r="L15" s="17"/>
-      <c r="M15" s="17"/>
-      <c r="N15" s="17"/>
-      <c r="O15" s="17"/>
-      <c r="P15" s="18"/>
-      <c r="Q15" s="18"/>
-      <c r="R15" s="18"/>
-      <c r="S15" s="18"/>
-      <c r="T15" s="18"/>
-      <c r="U15" s="18"/>
-      <c r="V15" s="19"/>
-      <c r="W15" s="19"/>
-      <c r="X15" s="19"/>
-      <c r="Y15" s="19"/>
-      <c r="Z15" s="19"/>
-      <c r="AA15" s="19"/>
-      <c r="AB15" s="19"/>
-    </row>
-    <row r="16" spans="2:28" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B16" s="22"/>
+      <c r="N9" s="76"/>
+      <c r="O9" s="76"/>
+      <c r="P9" s="76"/>
+      <c r="Q9" s="76"/>
+      <c r="R9" s="76"/>
+      <c r="S9" s="77"/>
+      <c r="T9" s="77"/>
+      <c r="U9" s="77"/>
+      <c r="V9" s="77"/>
+      <c r="W9" s="77"/>
+      <c r="X9" s="77"/>
+      <c r="Y9" s="77"/>
+    </row>
+    <row r="10" spans="2:25" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="B10" s="81" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="81" t="s">
+        <v>85</v>
+      </c>
+      <c r="D10" s="82" t="s">
+        <v>86</v>
+      </c>
+      <c r="E10" s="83" t="s">
+        <v>89</v>
+      </c>
+      <c r="F10" s="84" t="s">
+        <v>88</v>
+      </c>
+      <c r="G10" s="84"/>
+      <c r="H10" s="84"/>
+      <c r="I10" s="84"/>
+      <c r="J10" s="84"/>
+      <c r="K10" s="84"/>
+      <c r="L10" s="84" t="s">
+        <v>88</v>
+      </c>
+      <c r="M10" s="84"/>
+      <c r="N10" s="85" t="s">
+        <v>88</v>
+      </c>
+      <c r="O10" s="85"/>
+      <c r="P10" s="85"/>
+      <c r="Q10" s="85"/>
+      <c r="R10" s="85"/>
+      <c r="S10" s="86"/>
+      <c r="T10" s="86" t="s">
+        <v>88</v>
+      </c>
+      <c r="U10" s="86"/>
+      <c r="V10" s="86"/>
+      <c r="W10" s="86"/>
+      <c r="X10" s="86"/>
+      <c r="Y10" s="86"/>
+    </row>
+    <row r="11" spans="2:25" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="B11" s="81" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="81" t="s">
+        <v>90</v>
+      </c>
+      <c r="D11" s="82" t="s">
+        <v>86</v>
+      </c>
+      <c r="E11" s="83" t="s">
+        <v>89</v>
+      </c>
+      <c r="F11" s="84" t="s">
+        <v>88</v>
+      </c>
+      <c r="G11" s="84"/>
+      <c r="H11" s="84"/>
+      <c r="I11" s="84"/>
+      <c r="J11" s="84"/>
+      <c r="K11" s="84"/>
+      <c r="L11" s="84" t="s">
+        <v>88</v>
+      </c>
+      <c r="M11" s="84"/>
+      <c r="N11" s="85" t="s">
+        <v>88</v>
+      </c>
+      <c r="O11" s="85"/>
+      <c r="P11" s="85"/>
+      <c r="Q11" s="85"/>
+      <c r="R11" s="85"/>
+      <c r="S11" s="86"/>
+      <c r="T11" s="86" t="s">
+        <v>88</v>
+      </c>
+      <c r="U11" s="86"/>
+      <c r="V11" s="86"/>
+      <c r="W11" s="86"/>
+      <c r="X11" s="86"/>
+      <c r="Y11" s="86"/>
+    </row>
+    <row r="12" spans="2:25" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="B12" s="81" t="s">
+        <v>94</v>
+      </c>
+      <c r="C12" s="82">
+        <v>102</v>
+      </c>
+      <c r="D12" s="82" t="s">
+        <v>109</v>
+      </c>
+      <c r="E12" s="83" t="s">
+        <v>91</v>
+      </c>
+      <c r="F12" s="84"/>
+      <c r="G12" s="84" t="s">
+        <v>88</v>
+      </c>
+      <c r="H12" s="84" t="s">
+        <v>88</v>
+      </c>
+      <c r="I12" s="84"/>
+      <c r="J12" s="84"/>
+      <c r="K12" s="84"/>
+      <c r="L12" s="84" t="s">
+        <v>88</v>
+      </c>
+      <c r="M12" s="84"/>
+      <c r="N12" s="85"/>
+      <c r="O12" s="85" t="s">
+        <v>88</v>
+      </c>
+      <c r="P12" s="85"/>
+      <c r="Q12" s="85"/>
+      <c r="R12" s="85"/>
+      <c r="S12" s="86"/>
+      <c r="T12" s="86"/>
+      <c r="U12" s="86" t="s">
+        <v>88</v>
+      </c>
+      <c r="V12" s="86"/>
+      <c r="W12" s="86"/>
+      <c r="X12" s="86"/>
+      <c r="Y12" s="86"/>
+    </row>
+    <row r="13" spans="2:25" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="B13" s="81" t="s">
+        <v>95</v>
+      </c>
+      <c r="C13" s="81" t="s">
+        <v>93</v>
+      </c>
+      <c r="D13" s="82" t="s">
+        <v>96</v>
+      </c>
+      <c r="E13" s="83" t="s">
+        <v>97</v>
+      </c>
+      <c r="F13" s="84"/>
+      <c r="G13" s="84" t="s">
+        <v>88</v>
+      </c>
+      <c r="H13" s="84"/>
+      <c r="I13" s="84" t="s">
+        <v>88</v>
+      </c>
+      <c r="J13" s="84"/>
+      <c r="K13" s="84" t="s">
+        <v>88</v>
+      </c>
+      <c r="L13" s="84" t="s">
+        <v>88</v>
+      </c>
+      <c r="M13" s="84"/>
+      <c r="N13" s="85"/>
+      <c r="O13" s="85"/>
+      <c r="P13" s="85"/>
+      <c r="Q13" s="85"/>
+      <c r="R13" s="85" t="s">
+        <v>88</v>
+      </c>
+      <c r="S13" s="86"/>
+      <c r="T13" s="86"/>
+      <c r="U13" s="86"/>
+      <c r="V13" s="86"/>
+      <c r="W13" s="86" t="s">
+        <v>88</v>
+      </c>
+      <c r="X13" s="86"/>
+      <c r="Y13" s="86"/>
+    </row>
+    <row r="14" spans="2:25" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="B14" s="81" t="s">
+        <v>101</v>
+      </c>
+      <c r="C14" s="81" t="s">
+        <v>100</v>
+      </c>
+      <c r="D14" s="82" t="s">
+        <v>86</v>
+      </c>
+      <c r="E14" s="83" t="s">
+        <v>89</v>
+      </c>
+      <c r="F14" s="84" t="s">
+        <v>88</v>
+      </c>
+      <c r="G14" s="84"/>
+      <c r="H14" s="84"/>
+      <c r="I14" s="84"/>
+      <c r="J14" s="84"/>
+      <c r="K14" s="84"/>
+      <c r="L14" s="84" t="s">
+        <v>88</v>
+      </c>
+      <c r="M14" s="84"/>
+      <c r="N14" s="85" t="s">
+        <v>88</v>
+      </c>
+      <c r="O14" s="85"/>
+      <c r="P14" s="85"/>
+      <c r="Q14" s="85"/>
+      <c r="R14" s="85"/>
+      <c r="S14" s="86"/>
+      <c r="T14" s="86" t="s">
+        <v>88</v>
+      </c>
+      <c r="U14" s="86"/>
+      <c r="V14" s="86"/>
+      <c r="W14" s="86"/>
+      <c r="X14" s="86"/>
+      <c r="Y14" s="86"/>
+    </row>
+    <row r="15" spans="2:25" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="B15" s="81" t="s">
+        <v>102</v>
+      </c>
+      <c r="C15" s="81" t="s">
+        <v>103</v>
+      </c>
+      <c r="D15" s="82" t="s">
+        <v>104</v>
+      </c>
+      <c r="E15" s="83" t="s">
+        <v>105</v>
+      </c>
+      <c r="F15" s="84"/>
+      <c r="G15" s="84"/>
+      <c r="H15" s="84"/>
+      <c r="I15" s="84"/>
+      <c r="J15" s="84"/>
+      <c r="K15" s="84"/>
+      <c r="L15" s="84"/>
+      <c r="M15" s="84" t="s">
+        <v>88</v>
+      </c>
+      <c r="N15" s="85"/>
+      <c r="O15" s="85"/>
+      <c r="P15" s="85"/>
+      <c r="Q15" s="85" t="s">
+        <v>88</v>
+      </c>
+      <c r="R15" s="85"/>
+      <c r="S15" s="86" t="s">
+        <v>88</v>
+      </c>
+      <c r="T15" s="86"/>
+      <c r="U15" s="86"/>
+      <c r="V15" s="86"/>
+      <c r="W15" s="86"/>
+      <c r="X15" s="86"/>
+      <c r="Y15" s="86"/>
+    </row>
+    <row r="16" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B16" s="81" t="s">
+        <v>106</v>
+      </c>
+      <c r="C16" s="81" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" s="82" t="s">
+        <v>107</v>
+      </c>
+      <c r="E16" s="83" t="s">
+        <v>108</v>
+      </c>
+      <c r="F16" s="84"/>
+      <c r="G16" s="84" t="s">
+        <v>88</v>
+      </c>
+      <c r="H16" s="84"/>
+      <c r="I16" s="84"/>
+      <c r="J16" s="84"/>
+      <c r="K16" s="84"/>
+      <c r="L16" s="84" t="s">
+        <v>88</v>
+      </c>
+      <c r="M16" s="84"/>
+      <c r="N16" s="85"/>
+      <c r="O16" s="85"/>
+      <c r="P16" s="85"/>
+      <c r="Q16" s="85"/>
+      <c r="R16" s="85"/>
+      <c r="S16" s="86"/>
+      <c r="T16" s="86" t="s">
+        <v>88</v>
+      </c>
+      <c r="U16" s="86"/>
+      <c r="V16" s="86"/>
+      <c r="W16" s="86"/>
+      <c r="X16" s="86"/>
+      <c r="Y16" s="86"/>
     </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="28">
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="F7:M7"/>
+    <mergeCell ref="N7:R7"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="Q8:Q9"/>
     <mergeCell ref="D1:G1"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B6:B9"/>
     <mergeCell ref="C6:C7"/>
     <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:AB6"/>
-    <mergeCell ref="Z8:Z9"/>
-    <mergeCell ref="AA8:AA9"/>
-    <mergeCell ref="U8:U9"/>
+    <mergeCell ref="E6:Y6"/>
+    <mergeCell ref="W8:W9"/>
+    <mergeCell ref="X8:X9"/>
     <mergeCell ref="D8:D9"/>
     <mergeCell ref="F8:G8"/>
-    <mergeCell ref="W8:W9"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="Y8:Y9"/>
     <mergeCell ref="T8:T9"/>
-    <mergeCell ref="V7:AB7"/>
-    <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="U8:U9"/>
     <mergeCell ref="V8:V9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="Q8:Q9"/>
     <mergeCell ref="R8:R9"/>
-    <mergeCell ref="S8:S9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="F7:O7"/>
-    <mergeCell ref="P7:U7"/>
+    <mergeCell ref="S7:Y7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2792,89 +2973,84 @@
   <sheetPr>
     <tabColor theme="3" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B1:N16"/>
+  <dimension ref="B1:N22"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="7.21875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.21875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.109375" customWidth="1"/>
+    <col min="5" max="5" width="41.21875" customWidth="1"/>
+    <col min="6" max="6" width="16.109375" customWidth="1"/>
+    <col min="7" max="7" width="7.77734375" customWidth="1"/>
+    <col min="8" max="8" width="10" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="8.88671875" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="7.21875" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="41" customWidth="1"/>
+    <col min="12" max="12" width="35.5546875" customWidth="1"/>
     <col min="13" max="13" width="16.109375" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B1" s="12"/>
-      <c r="D1" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="40"/>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B3" s="80" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="80"/>
-      <c r="I3" s="80"/>
-      <c r="J3" s="80"/>
-      <c r="K3" s="80"/>
-      <c r="L3" s="80"/>
-    </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B4" s="81" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="91" t="s">
+      <c r="D1" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="29"/>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B3" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="83" t="s">
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
+      <c r="J3" s="38"/>
+      <c r="K3" s="38"/>
+      <c r="L3" s="38"/>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B4" s="39" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="48" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="89"/>
-      <c r="G4" s="89"/>
-      <c r="H4" s="89"/>
-      <c r="I4" s="89"/>
-      <c r="J4" s="84"/>
-      <c r="K4" s="83" t="s">
+      <c r="F4" s="45"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="45"/>
+      <c r="I4" s="45"/>
+      <c r="J4" s="42"/>
+      <c r="K4" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="L4" s="84"/>
-    </row>
-    <row r="5" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="82"/>
-      <c r="C5" s="90"/>
-      <c r="D5" s="92"/>
+      <c r="L4" s="42"/>
+    </row>
+    <row r="5" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="40"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="49"/>
       <c r="E5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="I5" s="85" t="s">
-        <v>1</v>
-      </c>
-      <c r="J5" s="86"/>
+        <v>112</v>
+      </c>
+      <c r="F5" s="43" t="s">
+        <v>83</v>
+      </c>
+      <c r="G5" s="89"/>
+      <c r="H5" s="89"/>
+      <c r="I5" s="89"/>
+      <c r="J5" s="44"/>
       <c r="K5" s="2" t="s">
         <v>4</v>
       </c>
@@ -2882,332 +3058,337 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="2:14" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="23">
+    <row r="6" spans="2:12" ht="15.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="13">
         <v>9</v>
       </c>
       <c r="C6" s="87" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E6" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F6" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G6" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="H6" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="I6" s="93" t="s">
-        <v>1</v>
-      </c>
-      <c r="J6" s="94"/>
-      <c r="K6" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="L6" s="23" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B7" s="23">
+        <v>43</v>
+      </c>
+      <c r="E6" s="90" t="s">
+        <v>113</v>
+      </c>
+      <c r="F6" s="91" t="s">
+        <v>85</v>
+      </c>
+      <c r="G6" s="92"/>
+      <c r="H6" s="92"/>
+      <c r="I6" s="92"/>
+      <c r="J6" s="93"/>
+      <c r="K6" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="L6" s="13" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="13">
         <v>10</v>
       </c>
-      <c r="C7" s="87"/>
+      <c r="C7" s="88"/>
       <c r="D7" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E7" s="23">
-        <v>5</v>
-      </c>
-      <c r="F7" s="23">
-        <v>6</v>
-      </c>
-      <c r="G7" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="H7" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I7" s="83" t="s">
-        <v>1</v>
-      </c>
-      <c r="J7" s="84"/>
-      <c r="K7" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="L7" s="23" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B8" s="23">
+        <v>44</v>
+      </c>
+      <c r="E7" s="95"/>
+      <c r="F7" s="91" t="s">
+        <v>90</v>
+      </c>
+      <c r="G7" s="92"/>
+      <c r="H7" s="92"/>
+      <c r="I7" s="92"/>
+      <c r="J7" s="93"/>
+      <c r="K7" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="L7" s="13" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="13">
         <v>11</v>
       </c>
-      <c r="C8" s="87"/>
+      <c r="C8" s="88"/>
       <c r="D8" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="E8" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F8" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G8" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="H8" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I8" s="83" t="s">
-        <v>1</v>
-      </c>
-      <c r="J8" s="84"/>
-      <c r="K8" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="L8" s="23" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B9" s="23">
+        <v>94</v>
+      </c>
+      <c r="E8" s="95"/>
+      <c r="F8" s="91">
+        <v>102</v>
+      </c>
+      <c r="G8" s="92"/>
+      <c r="H8" s="92"/>
+      <c r="I8" s="92"/>
+      <c r="J8" s="93"/>
+      <c r="K8" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="L8" s="13" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="13">
         <v>12</v>
       </c>
-      <c r="C9" s="87"/>
+      <c r="C9" s="88"/>
       <c r="D9" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="E9" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F9" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G9" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="H9" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="I9" s="83" t="s">
-        <v>1</v>
-      </c>
-      <c r="J9" s="84"/>
-      <c r="K9" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="L9" s="23" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>95</v>
+      </c>
+      <c r="E9" s="95"/>
+      <c r="F9" s="91" t="s">
+        <v>93</v>
+      </c>
+      <c r="G9" s="92"/>
+      <c r="H9" s="92"/>
+      <c r="I9" s="92"/>
+      <c r="J9" s="93"/>
+      <c r="K9" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="L9" s="13" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="2">
         <v>13</v>
       </c>
       <c r="C10" s="88"/>
       <c r="D10" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="E10" s="95"/>
+      <c r="F10" s="91" t="s">
+        <v>100</v>
+      </c>
+      <c r="G10" s="92"/>
+      <c r="H10" s="92"/>
+      <c r="I10" s="92"/>
+      <c r="J10" s="93"/>
+      <c r="K10" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="13">
+        <v>14</v>
+      </c>
+      <c r="C11" s="88"/>
+      <c r="D11" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="E11" s="95"/>
+      <c r="F11" s="91" t="s">
+        <v>96</v>
+      </c>
+      <c r="G11" s="92"/>
+      <c r="H11" s="92"/>
+      <c r="I11" s="92"/>
+      <c r="J11" s="93"/>
+      <c r="K11" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="L11" s="13" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="2">
+        <v>15</v>
+      </c>
+      <c r="C12" s="88"/>
+      <c r="D12" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="E12" s="94" t="s">
+        <v>114</v>
+      </c>
+      <c r="F12" s="91" t="s">
+        <v>85</v>
+      </c>
+      <c r="G12" s="92"/>
+      <c r="H12" s="92"/>
+      <c r="I12" s="92"/>
+      <c r="J12" s="93"/>
+      <c r="K12" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B18" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K18" s="15"/>
+    </row>
+    <row r="19" spans="2:14" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="50" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19" s="51"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="51"/>
+      <c r="F19" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="G19" s="53"/>
+      <c r="H19" s="50" t="s">
+        <v>59</v>
+      </c>
+      <c r="I19" s="51"/>
+      <c r="J19" s="51"/>
+      <c r="K19" s="51"/>
+      <c r="L19" s="67"/>
+      <c r="M19" s="36" t="s">
+        <v>60</v>
+      </c>
+      <c r="N19" s="37"/>
+    </row>
+    <row r="20" spans="2:14" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="62" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="D20" s="58" t="s">
+        <v>37</v>
+      </c>
+      <c r="E20" s="64" t="s">
+        <v>61</v>
+      </c>
+      <c r="F20" s="55" t="s">
+        <v>62</v>
+      </c>
+      <c r="G20" s="54" t="s">
+        <v>63</v>
+      </c>
+      <c r="H20" s="56" t="s">
+        <v>64</v>
+      </c>
+      <c r="I20" s="58" t="s">
+        <v>35</v>
+      </c>
+      <c r="J20" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="K20" s="60" t="s">
+        <v>38</v>
+      </c>
+      <c r="L20" s="68" t="s">
+        <v>65</v>
+      </c>
+      <c r="M20" s="70" t="s">
+        <v>66</v>
+      </c>
+      <c r="N20" s="46" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B21" s="63"/>
+      <c r="C21" s="59"/>
+      <c r="D21" s="59"/>
+      <c r="E21" s="65"/>
+      <c r="F21" s="66"/>
+      <c r="G21" s="54"/>
+      <c r="H21" s="57"/>
+      <c r="I21" s="59"/>
+      <c r="J21" s="59"/>
+      <c r="K21" s="61"/>
+      <c r="L21" s="69"/>
+      <c r="M21" s="62"/>
+      <c r="N21" s="55"/>
+    </row>
+    <row r="22" spans="2:14" ht="144" x14ac:dyDescent="0.3">
+      <c r="B22" s="17">
+        <v>7</v>
+      </c>
+      <c r="C22" s="16">
+        <v>5</v>
+      </c>
+      <c r="D22" s="16">
+        <v>2</v>
+      </c>
+      <c r="E22" s="96">
         <v>1</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="F22" s="98" t="s">
+        <v>119</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="I22" s="17">
+        <f>SUM(J22:K22)</f>
+        <v>0</v>
+      </c>
+      <c r="J22" s="16">
+        <v>0</v>
+      </c>
+      <c r="K22" s="18">
+        <v>0</v>
+      </c>
+      <c r="L22" s="97">
         <v>1</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="I10" s="85" t="s">
-        <v>1</v>
-      </c>
-      <c r="J10" s="86"/>
-      <c r="K10" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="2:14" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K12" s="25"/>
-    </row>
-    <row r="13" spans="2:14" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="56" t="s">
-        <v>66</v>
-      </c>
-      <c r="C13" s="57"/>
-      <c r="D13" s="57"/>
-      <c r="E13" s="57"/>
-      <c r="F13" s="58" t="s">
-        <v>67</v>
-      </c>
-      <c r="G13" s="59"/>
-      <c r="H13" s="56" t="s">
-        <v>68</v>
-      </c>
-      <c r="I13" s="57"/>
-      <c r="J13" s="57"/>
-      <c r="K13" s="57"/>
-      <c r="L13" s="74"/>
-      <c r="M13" s="78" t="s">
-        <v>69</v>
-      </c>
-      <c r="N13" s="79"/>
-    </row>
-    <row r="14" spans="2:14" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="69" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" s="65" t="s">
-        <v>38</v>
-      </c>
-      <c r="D14" s="65" t="s">
-        <v>39</v>
-      </c>
-      <c r="E14" s="71" t="s">
-        <v>70</v>
-      </c>
-      <c r="F14" s="62" t="s">
-        <v>71</v>
-      </c>
-      <c r="G14" s="60" t="s">
-        <v>72</v>
-      </c>
-      <c r="H14" s="63" t="s">
-        <v>73</v>
-      </c>
-      <c r="I14" s="65" t="s">
-        <v>37</v>
-      </c>
-      <c r="J14" s="65" t="s">
-        <v>38</v>
-      </c>
-      <c r="K14" s="67" t="s">
-        <v>40</v>
-      </c>
-      <c r="L14" s="75" t="s">
-        <v>74</v>
-      </c>
-      <c r="M14" s="77" t="s">
-        <v>75</v>
-      </c>
-      <c r="N14" s="61" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B15" s="70"/>
-      <c r="C15" s="66"/>
-      <c r="D15" s="66"/>
-      <c r="E15" s="72"/>
-      <c r="F15" s="73"/>
-      <c r="G15" s="60"/>
-      <c r="H15" s="64"/>
-      <c r="I15" s="66"/>
-      <c r="J15" s="66"/>
-      <c r="K15" s="68"/>
-      <c r="L15" s="76"/>
-      <c r="M15" s="69"/>
-      <c r="N15" s="62"/>
-    </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B16" s="29">
-        <f>SUM(C16:D16)</f>
-        <v>0</v>
-      </c>
-      <c r="C16" s="26">
-        <v>0</v>
-      </c>
-      <c r="D16" s="26">
-        <v>0</v>
-      </c>
-      <c r="E16" s="27"/>
-      <c r="F16" s="28"/>
-      <c r="G16" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="I16" s="29">
-        <f>SUM(J16:K16)</f>
-        <v>0</v>
-      </c>
-      <c r="J16" s="26">
-        <v>0</v>
-      </c>
-      <c r="K16" s="30">
-        <v>0</v>
-      </c>
-      <c r="L16" s="31"/>
-      <c r="M16" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="N16" s="32">
-        <f>C16</f>
-        <v>0</v>
+      <c r="M22" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="N22" s="19">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="31">
-    <mergeCell ref="M13:N13"/>
+  <mergeCells count="34">
+    <mergeCell ref="C6:C12"/>
+    <mergeCell ref="F5:J5"/>
+    <mergeCell ref="F6:J6"/>
+    <mergeCell ref="F7:J7"/>
+    <mergeCell ref="F8:J8"/>
+    <mergeCell ref="F9:J9"/>
+    <mergeCell ref="F10:J10"/>
+    <mergeCell ref="F11:J11"/>
+    <mergeCell ref="F12:J12"/>
+    <mergeCell ref="E6:E11"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="N20:N21"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="I20:I21"/>
+    <mergeCell ref="K20:K21"/>
+    <mergeCell ref="J20:J21"/>
+    <mergeCell ref="H19:L19"/>
+    <mergeCell ref="L20:L21"/>
+    <mergeCell ref="M20:M21"/>
+    <mergeCell ref="M19:N19"/>
     <mergeCell ref="D1:G1"/>
     <mergeCell ref="B3:L3"/>
     <mergeCell ref="B4:B5"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="I5:J5"/>
     <mergeCell ref="K4:L4"/>
-    <mergeCell ref="C6:C10"/>
     <mergeCell ref="E4:J4"/>
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="D4:D5"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="B13:E13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="N14:N15"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="H13:L13"/>
-    <mergeCell ref="L14:L15"/>
-    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="B19:E19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3215,21 +3396,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010058284A30843C9F43BD758DDD8294D484" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="6d50638930d08c51b5585735b2be047e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fed1744a-f275-4023-9290-77fd546fd730" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4acb07121b76573bb3c966f3dcb1b903" ns2:_="">
     <xsd:import namespace="fed1744a-f275-4023-9290-77fd546fd730"/>
@@ -3373,24 +3539,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6597AB9C-DC10-4824-8900-518D3B18165A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5426D20B-58AE-4BE9-8733-DFB2BC19D8C6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{741A764F-DFF5-4AE4-B0E7-77BD148FABB8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3406,4 +3570,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5426D20B-58AE-4BE9-8733-DFB2BC19D8C6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6597AB9C-DC10-4824-8900-518D3B18165A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Docs/Lab03/Lab03_WBT_TCs_Form.xlsx
+++ b/Docs/Lab03/Lab03_WBT_TCs_Form.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CCDDECC-D725-458A-A157-DA7FCE92B656}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{562C1F17-AFC9-4FC7-9A1B-B84580A1E8F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Statement" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="122">
   <si>
     <t>Informaţiile vor fi preluate din fişiere text.</t>
   </si>
@@ -551,6 +551,9 @@
   </si>
   <si>
     <t>da</t>
+  </si>
+  <si>
+    <t>F02_P05(impossible)</t>
   </si>
 </sst>
 </file>
@@ -1290,168 +1293,9 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1470,37 +1314,196 @@
     <xf numFmtId="0" fontId="15" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1933,12 +1936,12 @@
   <sheetData>
     <row r="1" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B1" s="12"/>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="38" t="s">
         <v>69</v>
       </c>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="29"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="40"/>
     </row>
     <row r="2" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B2" s="24" t="s">
@@ -2074,79 +2077,79 @@
   <sheetData>
     <row r="1" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B1" s="12"/>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="38" t="s">
         <v>69</v>
       </c>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="29"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="40"/>
     </row>
     <row r="3" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B3" s="33" t="s">
+      <c r="B3" s="43" t="s">
         <v>73</v>
       </c>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
-      <c r="K3" s="35"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="44"/>
+      <c r="H3" s="44"/>
+      <c r="I3" s="44"/>
+      <c r="J3" s="44"/>
+      <c r="K3" s="45"/>
     </row>
     <row r="6" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="28"/>
-      <c r="D6" s="28"/>
-      <c r="E6" s="28"/>
-      <c r="Q6" s="27"/>
-      <c r="R6" s="28"/>
-      <c r="S6" s="28"/>
-      <c r="T6" s="28"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="39"/>
+      <c r="Q6" s="38"/>
+      <c r="R6" s="39"/>
+      <c r="S6" s="39"/>
+      <c r="T6" s="39"/>
     </row>
     <row r="8" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B8" s="31" t="s">
+      <c r="B8" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="42"/>
       <c r="E8" s="21">
         <v>5</v>
       </c>
       <c r="I8" s="12"/>
-      <c r="Q8" s="31"/>
-      <c r="R8" s="31"/>
-      <c r="S8" s="31"/>
+      <c r="Q8" s="42"/>
+      <c r="R8" s="42"/>
+      <c r="S8" s="42"/>
       <c r="T8" s="21"/>
     </row>
     <row r="9" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B9" s="31" t="s">
+      <c r="B9" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="42"/>
       <c r="E9" s="21" t="s">
         <v>74</v>
       </c>
       <c r="I9" s="23"/>
-      <c r="Q9" s="31"/>
-      <c r="R9" s="31"/>
-      <c r="S9" s="31"/>
+      <c r="Q9" s="42"/>
+      <c r="R9" s="42"/>
+      <c r="S9" s="42"/>
       <c r="T9" s="21"/>
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B10" s="31" t="s">
+      <c r="B10" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="31" t="s">
+      <c r="C10" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="31"/>
+      <c r="D10" s="42"/>
       <c r="E10" s="21" t="s">
         <v>75</v>
       </c>
@@ -2157,9 +2160,9 @@
       <c r="M10" s="26"/>
       <c r="N10" s="26"/>
       <c r="O10" s="26"/>
-      <c r="Q10" s="31"/>
-      <c r="R10" s="31"/>
-      <c r="S10" s="31"/>
+      <c r="Q10" s="42"/>
+      <c r="R10" s="42"/>
+      <c r="S10" s="42"/>
       <c r="T10" s="21"/>
     </row>
     <row r="11" spans="2:20" x14ac:dyDescent="0.3">
@@ -2181,12 +2184,12 @@
       <c r="O12" s="26"/>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.3">
-      <c r="B13" s="27" t="s">
+      <c r="B13" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
+      <c r="C13" s="39"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="39"/>
       <c r="I13" s="26"/>
       <c r="J13" s="26"/>
       <c r="K13" s="26"/>
@@ -2194,10 +2197,10 @@
       <c r="M13" s="26"/>
       <c r="N13" s="26"/>
       <c r="O13" s="26"/>
-      <c r="Q13" s="27"/>
-      <c r="R13" s="28"/>
-      <c r="S13" s="28"/>
-      <c r="T13" s="28"/>
+      <c r="Q13" s="38"/>
+      <c r="R13" s="39"/>
+      <c r="S13" s="39"/>
+      <c r="T13" s="39"/>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.3">
       <c r="I14" s="26"/>
@@ -2212,11 +2215,11 @@
       <c r="B15" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="32" t="s">
+      <c r="C15" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="D15" s="32"/>
-      <c r="E15" s="32"/>
+      <c r="D15" s="46"/>
+      <c r="E15" s="46"/>
       <c r="I15" s="26"/>
       <c r="J15" s="26"/>
       <c r="K15" s="26"/>
@@ -2225,19 +2228,19 @@
       <c r="N15" s="26"/>
       <c r="O15" s="26"/>
       <c r="Q15" s="20"/>
-      <c r="R15" s="32"/>
-      <c r="S15" s="32"/>
-      <c r="T15" s="32"/>
+      <c r="R15" s="46"/>
+      <c r="S15" s="46"/>
+      <c r="T15" s="46"/>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B16" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="C16" s="30" t="s">
+      <c r="C16" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="41"/>
       <c r="I16" s="26"/>
       <c r="J16" s="26"/>
       <c r="K16" s="26"/>
@@ -2246,19 +2249,19 @@
       <c r="N16" s="26"/>
       <c r="O16" s="26"/>
       <c r="Q16" s="22"/>
-      <c r="R16" s="30"/>
-      <c r="S16" s="30"/>
-      <c r="T16" s="30"/>
+      <c r="R16" s="41"/>
+      <c r="S16" s="41"/>
+      <c r="T16" s="41"/>
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B17" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="C17" s="30" t="s">
+      <c r="C17" s="41" t="s">
         <v>77</v>
       </c>
-      <c r="D17" s="30"/>
-      <c r="E17" s="30"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="41"/>
       <c r="I17" s="26"/>
       <c r="J17" s="26"/>
       <c r="K17" s="26"/>
@@ -2267,19 +2270,19 @@
       <c r="N17" s="26"/>
       <c r="O17" s="26"/>
       <c r="Q17" s="22"/>
-      <c r="R17" s="30"/>
-      <c r="S17" s="30"/>
-      <c r="T17" s="30"/>
+      <c r="R17" s="41"/>
+      <c r="S17" s="41"/>
+      <c r="T17" s="41"/>
     </row>
     <row r="18" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B18" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="C18" s="30" t="s">
+      <c r="C18" s="41" t="s">
         <v>78</v>
       </c>
-      <c r="D18" s="30"/>
-      <c r="E18" s="30"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="41"/>
       <c r="I18" s="26"/>
       <c r="J18" s="26"/>
       <c r="K18" s="26"/>
@@ -2288,19 +2291,19 @@
       <c r="N18" s="26"/>
       <c r="O18" s="26"/>
       <c r="Q18" s="22"/>
-      <c r="R18" s="30"/>
-      <c r="S18" s="30"/>
-      <c r="T18" s="30"/>
+      <c r="R18" s="41"/>
+      <c r="S18" s="41"/>
+      <c r="T18" s="41"/>
     </row>
     <row r="19" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B19" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="C19" s="30" t="s">
+      <c r="C19" s="41" t="s">
         <v>79</v>
       </c>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="41"/>
       <c r="I19" s="26"/>
       <c r="J19" s="26"/>
       <c r="K19" s="26"/>
@@ -2309,19 +2312,19 @@
       <c r="N19" s="26"/>
       <c r="O19" s="26"/>
       <c r="Q19" s="22"/>
-      <c r="R19" s="30"/>
-      <c r="S19" s="30"/>
-      <c r="T19" s="30"/>
+      <c r="R19" s="41"/>
+      <c r="S19" s="41"/>
+      <c r="T19" s="41"/>
     </row>
     <row r="20" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B20" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="C20" s="30" t="s">
+      <c r="C20" s="41" t="s">
         <v>81</v>
       </c>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="41"/>
       <c r="I20" s="26"/>
       <c r="J20" s="26"/>
       <c r="K20" s="26"/>
@@ -2330,26 +2333,26 @@
       <c r="N20" s="26"/>
       <c r="O20" s="26"/>
       <c r="Q20" s="22"/>
-      <c r="R20" s="30"/>
-      <c r="S20" s="30"/>
-      <c r="T20" s="30"/>
+      <c r="R20" s="41"/>
+      <c r="S20" s="41"/>
+      <c r="T20" s="41"/>
     </row>
     <row r="21" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B21" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="C21" s="30" t="s">
+      <c r="C21" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
+      <c r="D21" s="41"/>
+      <c r="E21" s="41"/>
       <c r="M21" s="26"/>
       <c r="N21" s="26"/>
       <c r="O21" s="26"/>
       <c r="Q21" s="22"/>
-      <c r="R21" s="30"/>
-      <c r="S21" s="30"/>
-      <c r="T21" s="30"/>
+      <c r="R21" s="41"/>
+      <c r="S21" s="41"/>
+      <c r="T21" s="41"/>
     </row>
     <row r="22" spans="2:20" x14ac:dyDescent="0.3">
       <c r="M22" s="26"/>
@@ -2375,26 +2378,18 @@
       <c r="O24" s="26"/>
     </row>
     <row r="61" spans="4:10" x14ac:dyDescent="0.3">
-      <c r="D61" s="27" t="s">
+      <c r="D61" s="38" t="s">
         <v>40</v>
       </c>
-      <c r="E61" s="28"/>
-      <c r="F61" s="28"/>
-      <c r="G61" s="28"/>
-      <c r="H61" s="28"/>
-      <c r="I61" s="28"/>
-      <c r="J61" s="28"/>
+      <c r="E61" s="39"/>
+      <c r="F61" s="39"/>
+      <c r="G61" s="39"/>
+      <c r="H61" s="39"/>
+      <c r="I61" s="39"/>
+      <c r="J61" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D61:J61"/>
-    <mergeCell ref="Q6:T6"/>
-    <mergeCell ref="R17:T17"/>
-    <mergeCell ref="R19:T19"/>
-    <mergeCell ref="R18:T18"/>
-    <mergeCell ref="Q9:S9"/>
-    <mergeCell ref="R16:T16"/>
-    <mergeCell ref="Q13:T13"/>
     <mergeCell ref="D1:I1"/>
     <mergeCell ref="R20:T20"/>
     <mergeCell ref="R21:T21"/>
@@ -2411,6 +2406,14 @@
     <mergeCell ref="C15:E15"/>
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="C17:E17"/>
+    <mergeCell ref="D61:J61"/>
+    <mergeCell ref="Q6:T6"/>
+    <mergeCell ref="R17:T17"/>
+    <mergeCell ref="R19:T19"/>
+    <mergeCell ref="R18:T18"/>
+    <mergeCell ref="Q9:S9"/>
+    <mergeCell ref="R16:T16"/>
+    <mergeCell ref="Q13:T13"/>
     <mergeCell ref="C18:E18"/>
     <mergeCell ref="C19:E19"/>
     <mergeCell ref="C20:E20"/>
@@ -2445,508 +2448,497 @@
   <sheetData>
     <row r="1" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B1" s="12"/>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="38" t="s">
         <v>69</v>
       </c>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="29"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="40"/>
     </row>
     <row r="3" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B3" s="33" t="s">
+      <c r="B3" s="43" t="s">
         <v>73</v>
       </c>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="35"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="45"/>
     </row>
     <row r="5" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B5" s="11"/>
     </row>
     <row r="6" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B6" s="71" t="s">
+      <c r="B6" s="53" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="71" t="s">
+      <c r="C6" s="53" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="72" t="s">
+      <c r="D6" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="71" t="s">
+      <c r="E6" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="71"/>
-      <c r="G6" s="71"/>
-      <c r="H6" s="71"/>
-      <c r="I6" s="71"/>
-      <c r="J6" s="71"/>
-      <c r="K6" s="71"/>
-      <c r="L6" s="71"/>
-      <c r="M6" s="71"/>
-      <c r="N6" s="71"/>
-      <c r="O6" s="71"/>
-      <c r="P6" s="71"/>
-      <c r="Q6" s="71"/>
-      <c r="R6" s="71"/>
-      <c r="S6" s="71"/>
-      <c r="T6" s="71"/>
-      <c r="U6" s="71"/>
-      <c r="V6" s="71"/>
-      <c r="W6" s="71"/>
-      <c r="X6" s="71"/>
-      <c r="Y6" s="71"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="53"/>
+      <c r="H6" s="53"/>
+      <c r="I6" s="53"/>
+      <c r="J6" s="53"/>
+      <c r="K6" s="53"/>
+      <c r="L6" s="53"/>
+      <c r="M6" s="53"/>
+      <c r="N6" s="53"/>
+      <c r="O6" s="53"/>
+      <c r="P6" s="53"/>
+      <c r="Q6" s="53"/>
+      <c r="R6" s="53"/>
+      <c r="S6" s="53"/>
+      <c r="T6" s="53"/>
+      <c r="U6" s="53"/>
+      <c r="V6" s="53"/>
+      <c r="W6" s="53"/>
+      <c r="X6" s="53"/>
+      <c r="Y6" s="53"/>
     </row>
     <row r="7" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B7" s="71"/>
-      <c r="C7" s="71"/>
-      <c r="D7" s="73"/>
-      <c r="E7" s="74" t="s">
+      <c r="B7" s="53"/>
+      <c r="C7" s="53"/>
+      <c r="D7" s="55"/>
+      <c r="E7" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="75" t="s">
+      <c r="F7" s="50" t="s">
         <v>31</v>
       </c>
-      <c r="G7" s="75"/>
-      <c r="H7" s="75"/>
-      <c r="I7" s="75"/>
-      <c r="J7" s="75"/>
-      <c r="K7" s="75"/>
-      <c r="L7" s="75"/>
-      <c r="M7" s="75"/>
-      <c r="N7" s="76" t="s">
+      <c r="G7" s="50"/>
+      <c r="H7" s="50"/>
+      <c r="I7" s="50"/>
+      <c r="J7" s="50"/>
+      <c r="K7" s="50"/>
+      <c r="L7" s="50"/>
+      <c r="M7" s="50"/>
+      <c r="N7" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="O7" s="76"/>
-      <c r="P7" s="76"/>
-      <c r="Q7" s="76"/>
-      <c r="R7" s="76"/>
-      <c r="S7" s="77" t="s">
+      <c r="O7" s="51"/>
+      <c r="P7" s="51"/>
+      <c r="Q7" s="51"/>
+      <c r="R7" s="51"/>
+      <c r="S7" s="52" t="s">
         <v>17</v>
       </c>
-      <c r="T7" s="77"/>
-      <c r="U7" s="77"/>
-      <c r="V7" s="77"/>
-      <c r="W7" s="77"/>
-      <c r="X7" s="77"/>
-      <c r="Y7" s="77"/>
+      <c r="T7" s="52"/>
+      <c r="U7" s="52"/>
+      <c r="V7" s="52"/>
+      <c r="W7" s="52"/>
+      <c r="X7" s="52"/>
+      <c r="Y7" s="52"/>
     </row>
     <row r="8" spans="2:25" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="71"/>
-      <c r="C8" s="78" t="s">
+      <c r="B8" s="53"/>
+      <c r="C8" s="47" t="s">
         <v>83</v>
       </c>
-      <c r="D8" s="78" t="s">
+      <c r="D8" s="47" t="s">
         <v>84</v>
       </c>
-      <c r="E8" s="74"/>
-      <c r="F8" s="75" t="s">
+      <c r="E8" s="49"/>
+      <c r="F8" s="50" t="s">
         <v>87</v>
       </c>
-      <c r="G8" s="75"/>
-      <c r="H8" s="75" t="s">
+      <c r="G8" s="50"/>
+      <c r="H8" s="50" t="s">
         <v>92</v>
       </c>
-      <c r="I8" s="75"/>
-      <c r="J8" s="75" t="s">
+      <c r="I8" s="50"/>
+      <c r="J8" s="50" t="s">
         <v>98</v>
       </c>
-      <c r="K8" s="75"/>
-      <c r="L8" s="75" t="s">
+      <c r="K8" s="50"/>
+      <c r="L8" s="50" t="s">
         <v>99</v>
       </c>
-      <c r="M8" s="75"/>
-      <c r="N8" s="76" t="s">
+      <c r="M8" s="50"/>
+      <c r="N8" s="51" t="s">
         <v>45</v>
       </c>
-      <c r="O8" s="76" t="s">
+      <c r="O8" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="P8" s="76" t="s">
+      <c r="P8" s="51" t="s">
         <v>47</v>
       </c>
-      <c r="Q8" s="76" t="s">
+      <c r="Q8" s="51" t="s">
         <v>80</v>
       </c>
-      <c r="R8" s="76" t="s">
-        <v>82</v>
-      </c>
-      <c r="S8" s="77">
+      <c r="R8" s="51" t="s">
+        <v>121</v>
+      </c>
+      <c r="S8" s="52">
         <v>0</v>
       </c>
-      <c r="T8" s="77">
+      <c r="T8" s="52">
         <v>1</v>
       </c>
-      <c r="U8" s="77">
+      <c r="U8" s="52">
         <v>2</v>
       </c>
-      <c r="V8" s="77" t="s">
+      <c r="V8" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="W8" s="77" t="s">
+      <c r="W8" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="X8" s="77" t="s">
+      <c r="X8" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="Y8" s="77" t="s">
+      <c r="Y8" s="52" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="9" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B9" s="71"/>
-      <c r="C9" s="79"/>
-      <c r="D9" s="79"/>
-      <c r="E9" s="74"/>
-      <c r="F9" s="80" t="s">
+      <c r="B9" s="53"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="80" t="s">
+      <c r="G9" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="H9" s="80" t="s">
+      <c r="H9" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="I9" s="80" t="s">
+      <c r="I9" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="J9" s="80" t="s">
+      <c r="J9" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="K9" s="80" t="s">
+      <c r="K9" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="L9" s="80" t="s">
+      <c r="L9" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="M9" s="80" t="s">
+      <c r="M9" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="N9" s="76"/>
-      <c r="O9" s="76"/>
-      <c r="P9" s="76"/>
-      <c r="Q9" s="76"/>
-      <c r="R9" s="76"/>
-      <c r="S9" s="77"/>
-      <c r="T9" s="77"/>
-      <c r="U9" s="77"/>
-      <c r="V9" s="77"/>
-      <c r="W9" s="77"/>
-      <c r="X9" s="77"/>
-      <c r="Y9" s="77"/>
+      <c r="N9" s="51"/>
+      <c r="O9" s="51"/>
+      <c r="P9" s="51"/>
+      <c r="Q9" s="51"/>
+      <c r="R9" s="51"/>
+      <c r="S9" s="52"/>
+      <c r="T9" s="52"/>
+      <c r="U9" s="52"/>
+      <c r="V9" s="52"/>
+      <c r="W9" s="52"/>
+      <c r="X9" s="52"/>
+      <c r="Y9" s="52"/>
     </row>
     <row r="10" spans="2:25" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="B10" s="81" t="s">
+      <c r="B10" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="81" t="s">
+      <c r="C10" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="D10" s="82" t="s">
+      <c r="D10" s="29" t="s">
         <v>86</v>
       </c>
-      <c r="E10" s="83" t="s">
+      <c r="E10" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="F10" s="84" t="s">
+      <c r="F10" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="G10" s="84"/>
-      <c r="H10" s="84"/>
-      <c r="I10" s="84"/>
-      <c r="J10" s="84"/>
-      <c r="K10" s="84"/>
-      <c r="L10" s="84" t="s">
+      <c r="G10" s="31"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="31"/>
+      <c r="K10" s="31"/>
+      <c r="L10" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="M10" s="84"/>
-      <c r="N10" s="85" t="s">
+      <c r="M10" s="31"/>
+      <c r="N10" s="32" t="s">
         <v>88</v>
       </c>
-      <c r="O10" s="85"/>
-      <c r="P10" s="85"/>
-      <c r="Q10" s="85"/>
-      <c r="R10" s="85"/>
-      <c r="S10" s="86"/>
-      <c r="T10" s="86" t="s">
+      <c r="O10" s="32"/>
+      <c r="P10" s="32"/>
+      <c r="Q10" s="32"/>
+      <c r="R10" s="32"/>
+      <c r="S10" s="33"/>
+      <c r="T10" s="33" t="s">
         <v>88</v>
       </c>
-      <c r="U10" s="86"/>
-      <c r="V10" s="86"/>
-      <c r="W10" s="86"/>
-      <c r="X10" s="86"/>
-      <c r="Y10" s="86"/>
+      <c r="U10" s="33"/>
+      <c r="V10" s="33"/>
+      <c r="W10" s="33"/>
+      <c r="X10" s="33"/>
+      <c r="Y10" s="33"/>
     </row>
     <row r="11" spans="2:25" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="B11" s="81" t="s">
+      <c r="B11" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="81" t="s">
+      <c r="C11" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="D11" s="82" t="s">
+      <c r="D11" s="29" t="s">
         <v>86</v>
       </c>
-      <c r="E11" s="83" t="s">
+      <c r="E11" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="F11" s="84" t="s">
+      <c r="F11" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="G11" s="84"/>
-      <c r="H11" s="84"/>
-      <c r="I11" s="84"/>
-      <c r="J11" s="84"/>
-      <c r="K11" s="84"/>
-      <c r="L11" s="84" t="s">
+      <c r="G11" s="31"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="31"/>
+      <c r="J11" s="31"/>
+      <c r="K11" s="31"/>
+      <c r="L11" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="M11" s="84"/>
-      <c r="N11" s="85" t="s">
+      <c r="M11" s="31"/>
+      <c r="N11" s="32" t="s">
         <v>88</v>
       </c>
-      <c r="O11" s="85"/>
-      <c r="P11" s="85"/>
-      <c r="Q11" s="85"/>
-      <c r="R11" s="85"/>
-      <c r="S11" s="86"/>
-      <c r="T11" s="86" t="s">
+      <c r="O11" s="32"/>
+      <c r="P11" s="32"/>
+      <c r="Q11" s="32"/>
+      <c r="R11" s="32"/>
+      <c r="S11" s="33"/>
+      <c r="T11" s="33" t="s">
         <v>88</v>
       </c>
-      <c r="U11" s="86"/>
-      <c r="V11" s="86"/>
-      <c r="W11" s="86"/>
-      <c r="X11" s="86"/>
-      <c r="Y11" s="86"/>
+      <c r="U11" s="33"/>
+      <c r="V11" s="33"/>
+      <c r="W11" s="33"/>
+      <c r="X11" s="33"/>
+      <c r="Y11" s="33"/>
     </row>
     <row r="12" spans="2:25" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="B12" s="81" t="s">
+      <c r="B12" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="C12" s="82">
+      <c r="C12" s="29">
         <v>102</v>
       </c>
-      <c r="D12" s="82" t="s">
+      <c r="D12" s="29" t="s">
         <v>109</v>
       </c>
-      <c r="E12" s="83" t="s">
+      <c r="E12" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="F12" s="84"/>
-      <c r="G12" s="84" t="s">
+      <c r="F12" s="31"/>
+      <c r="G12" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="H12" s="84" t="s">
+      <c r="H12" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="I12" s="84"/>
-      <c r="J12" s="84"/>
-      <c r="K12" s="84"/>
-      <c r="L12" s="84" t="s">
+      <c r="I12" s="31"/>
+      <c r="J12" s="31"/>
+      <c r="K12" s="31"/>
+      <c r="L12" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="M12" s="84"/>
-      <c r="N12" s="85"/>
-      <c r="O12" s="85" t="s">
+      <c r="M12" s="31"/>
+      <c r="N12" s="32"/>
+      <c r="O12" s="32" t="s">
         <v>88</v>
       </c>
-      <c r="P12" s="85"/>
-      <c r="Q12" s="85"/>
-      <c r="R12" s="85"/>
-      <c r="S12" s="86"/>
-      <c r="T12" s="86"/>
-      <c r="U12" s="86" t="s">
+      <c r="P12" s="32"/>
+      <c r="Q12" s="32"/>
+      <c r="R12" s="32"/>
+      <c r="S12" s="33"/>
+      <c r="T12" s="33"/>
+      <c r="U12" s="33" t="s">
         <v>88</v>
       </c>
-      <c r="V12" s="86"/>
-      <c r="W12" s="86"/>
-      <c r="X12" s="86"/>
-      <c r="Y12" s="86"/>
+      <c r="V12" s="33"/>
+      <c r="W12" s="33"/>
+      <c r="X12" s="33"/>
+      <c r="Y12" s="33"/>
     </row>
     <row r="13" spans="2:25" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="B13" s="81" t="s">
+      <c r="B13" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="C13" s="81" t="s">
+      <c r="C13" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="D13" s="82" t="s">
+      <c r="D13" s="29" t="s">
         <v>96</v>
       </c>
-      <c r="E13" s="83" t="s">
+      <c r="E13" s="30" t="s">
         <v>97</v>
       </c>
-      <c r="F13" s="84"/>
-      <c r="G13" s="84" t="s">
+      <c r="F13" s="31"/>
+      <c r="G13" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="H13" s="84"/>
-      <c r="I13" s="84" t="s">
+      <c r="H13" s="31"/>
+      <c r="I13" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="J13" s="84"/>
-      <c r="K13" s="84" t="s">
+      <c r="J13" s="31"/>
+      <c r="K13" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="L13" s="84" t="s">
+      <c r="L13" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="M13" s="84"/>
-      <c r="N13" s="85"/>
-      <c r="O13" s="85"/>
-      <c r="P13" s="85"/>
-      <c r="Q13" s="85"/>
-      <c r="R13" s="85" t="s">
+      <c r="M13" s="31"/>
+      <c r="N13" s="32"/>
+      <c r="O13" s="32"/>
+      <c r="P13" s="32" t="s">
         <v>88</v>
       </c>
-      <c r="S13" s="86"/>
-      <c r="T13" s="86"/>
-      <c r="U13" s="86"/>
-      <c r="V13" s="86"/>
-      <c r="W13" s="86" t="s">
+      <c r="Q13" s="32"/>
+      <c r="R13" s="32"/>
+      <c r="S13" s="33"/>
+      <c r="T13" s="33"/>
+      <c r="U13" s="33"/>
+      <c r="V13" s="33"/>
+      <c r="W13" s="33" t="s">
         <v>88</v>
       </c>
-      <c r="X13" s="86"/>
-      <c r="Y13" s="86"/>
+      <c r="X13" s="33"/>
+      <c r="Y13" s="33"/>
     </row>
     <row r="14" spans="2:25" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="B14" s="81" t="s">
+      <c r="B14" s="28" t="s">
         <v>101</v>
       </c>
-      <c r="C14" s="81" t="s">
+      <c r="C14" s="28" t="s">
         <v>100</v>
       </c>
-      <c r="D14" s="82" t="s">
+      <c r="D14" s="29" t="s">
         <v>86</v>
       </c>
-      <c r="E14" s="83" t="s">
+      <c r="E14" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="F14" s="84" t="s">
+      <c r="F14" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="G14" s="84"/>
-      <c r="H14" s="84"/>
-      <c r="I14" s="84"/>
-      <c r="J14" s="84"/>
-      <c r="K14" s="84"/>
-      <c r="L14" s="84" t="s">
+      <c r="G14" s="31"/>
+      <c r="H14" s="31"/>
+      <c r="I14" s="31"/>
+      <c r="J14" s="31"/>
+      <c r="K14" s="31"/>
+      <c r="L14" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="M14" s="84"/>
-      <c r="N14" s="85" t="s">
+      <c r="M14" s="31"/>
+      <c r="N14" s="32" t="s">
         <v>88</v>
       </c>
-      <c r="O14" s="85"/>
-      <c r="P14" s="85"/>
-      <c r="Q14" s="85"/>
-      <c r="R14" s="85"/>
-      <c r="S14" s="86"/>
-      <c r="T14" s="86" t="s">
+      <c r="O14" s="32"/>
+      <c r="P14" s="32"/>
+      <c r="Q14" s="32"/>
+      <c r="R14" s="32"/>
+      <c r="S14" s="33"/>
+      <c r="T14" s="33" t="s">
         <v>88</v>
       </c>
-      <c r="U14" s="86"/>
-      <c r="V14" s="86"/>
-      <c r="W14" s="86"/>
-      <c r="X14" s="86"/>
-      <c r="Y14" s="86"/>
+      <c r="U14" s="33"/>
+      <c r="V14" s="33"/>
+      <c r="W14" s="33"/>
+      <c r="X14" s="33"/>
+      <c r="Y14" s="33"/>
     </row>
     <row r="15" spans="2:25" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="B15" s="81" t="s">
+      <c r="B15" s="28" t="s">
         <v>102</v>
       </c>
-      <c r="C15" s="81" t="s">
+      <c r="C15" s="28" t="s">
         <v>103</v>
       </c>
-      <c r="D15" s="82" t="s">
+      <c r="D15" s="29" t="s">
         <v>104</v>
       </c>
-      <c r="E15" s="83" t="s">
+      <c r="E15" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="F15" s="84"/>
-      <c r="G15" s="84"/>
-      <c r="H15" s="84"/>
-      <c r="I15" s="84"/>
-      <c r="J15" s="84"/>
-      <c r="K15" s="84"/>
-      <c r="L15" s="84"/>
-      <c r="M15" s="84" t="s">
+      <c r="F15" s="31"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="31"/>
+      <c r="J15" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="N15" s="85"/>
-      <c r="O15" s="85"/>
-      <c r="P15" s="85"/>
-      <c r="Q15" s="85" t="s">
+      <c r="K15" s="31"/>
+      <c r="L15" s="31"/>
+      <c r="M15" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="R15" s="85"/>
-      <c r="S15" s="86" t="s">
+      <c r="N15" s="32"/>
+      <c r="O15" s="32"/>
+      <c r="P15" s="32"/>
+      <c r="Q15" s="32" t="s">
         <v>88</v>
       </c>
-      <c r="T15" s="86"/>
-      <c r="U15" s="86"/>
-      <c r="V15" s="86"/>
-      <c r="W15" s="86"/>
-      <c r="X15" s="86"/>
-      <c r="Y15" s="86"/>
+      <c r="R15" s="32"/>
+      <c r="S15" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="T15" s="33"/>
+      <c r="U15" s="33"/>
+      <c r="V15" s="33"/>
+      <c r="W15" s="33"/>
+      <c r="X15" s="33"/>
+      <c r="Y15" s="33"/>
     </row>
     <row r="16" spans="2:25" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B16" s="81" t="s">
+      <c r="B16" s="28" t="s">
         <v>106</v>
       </c>
-      <c r="C16" s="81" t="s">
+      <c r="C16" s="28" t="s">
         <v>96</v>
       </c>
-      <c r="D16" s="82" t="s">
+      <c r="D16" s="29" t="s">
         <v>107</v>
       </c>
-      <c r="E16" s="83" t="s">
+      <c r="E16" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="F16" s="84"/>
-      <c r="G16" s="84" t="s">
+      <c r="F16" s="31"/>
+      <c r="G16" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="H16" s="84"/>
-      <c r="I16" s="84"/>
-      <c r="J16" s="84"/>
-      <c r="K16" s="84"/>
-      <c r="L16" s="84" t="s">
+      <c r="H16" s="31"/>
+      <c r="I16" s="31"/>
+      <c r="J16" s="31"/>
+      <c r="K16" s="31"/>
+      <c r="L16" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="M16" s="84"/>
-      <c r="N16" s="85"/>
-      <c r="O16" s="85"/>
-      <c r="P16" s="85"/>
-      <c r="Q16" s="85"/>
-      <c r="R16" s="85"/>
-      <c r="S16" s="86"/>
-      <c r="T16" s="86" t="s">
+      <c r="M16" s="31"/>
+      <c r="N16" s="32"/>
+      <c r="O16" s="32"/>
+      <c r="P16" s="32"/>
+      <c r="Q16" s="32"/>
+      <c r="R16" s="32"/>
+      <c r="S16" s="33"/>
+      <c r="T16" s="33" t="s">
         <v>88</v>
       </c>
-      <c r="U16" s="86"/>
-      <c r="V16" s="86"/>
-      <c r="W16" s="86"/>
-      <c r="X16" s="86"/>
-      <c r="Y16" s="86"/>
+      <c r="U16" s="33"/>
+      <c r="V16" s="33"/>
+      <c r="W16" s="33"/>
+      <c r="X16" s="33"/>
+      <c r="Y16" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="F7:M7"/>
-    <mergeCell ref="N7:R7"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="S8:S9"/>
-    <mergeCell ref="N8:N9"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="Q8:Q9"/>
     <mergeCell ref="D1:G1"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B6:B9"/>
@@ -2962,6 +2954,19 @@
     <mergeCell ref="V8:V9"/>
     <mergeCell ref="R8:R9"/>
     <mergeCell ref="S7:Y7"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="F7:M7"/>
+    <mergeCell ref="N7:R7"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="Q8:Q9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2992,65 +2997,65 @@
   <sheetData>
     <row r="1" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B1" s="12"/>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="38" t="s">
         <v>69</v>
       </c>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="29"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="40"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="90" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="38"/>
-      <c r="L3" s="38"/>
+      <c r="C3" s="90"/>
+      <c r="D3" s="90"/>
+      <c r="E3" s="90"/>
+      <c r="F3" s="90"/>
+      <c r="G3" s="90"/>
+      <c r="H3" s="90"/>
+      <c r="I3" s="90"/>
+      <c r="J3" s="90"/>
+      <c r="K3" s="90"/>
+      <c r="L3" s="90"/>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="39" t="s">
+      <c r="B4" s="91" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="46" t="s">
+      <c r="C4" s="77" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="48" t="s">
+      <c r="D4" s="97" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="41" t="s">
+      <c r="E4" s="93" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="45"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="42"/>
-      <c r="K4" s="41" t="s">
+      <c r="F4" s="95"/>
+      <c r="G4" s="95"/>
+      <c r="H4" s="95"/>
+      <c r="I4" s="95"/>
+      <c r="J4" s="94"/>
+      <c r="K4" s="93" t="s">
         <v>3</v>
       </c>
-      <c r="L4" s="42"/>
+      <c r="L4" s="94"/>
     </row>
     <row r="5" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="40"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="49"/>
+      <c r="B5" s="92"/>
+      <c r="C5" s="96"/>
+      <c r="D5" s="98"/>
       <c r="E5" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="F5" s="43" t="s">
+      <c r="F5" s="58" t="s">
         <v>83</v>
       </c>
-      <c r="G5" s="89"/>
-      <c r="H5" s="89"/>
-      <c r="I5" s="89"/>
-      <c r="J5" s="44"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="60"/>
       <c r="K5" s="2" t="s">
         <v>4</v>
       </c>
@@ -3062,22 +3067,22 @@
       <c r="B6" s="13">
         <v>9</v>
       </c>
-      <c r="C6" s="87" t="s">
+      <c r="C6" s="56" t="s">
         <v>39</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="90" t="s">
+      <c r="E6" s="64" t="s">
         <v>113</v>
       </c>
-      <c r="F6" s="91" t="s">
+      <c r="F6" s="61" t="s">
         <v>85</v>
       </c>
-      <c r="G6" s="92"/>
-      <c r="H6" s="92"/>
-      <c r="I6" s="92"/>
-      <c r="J6" s="93"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="63"/>
       <c r="K6" s="14" t="s">
         <v>115</v>
       </c>
@@ -3089,18 +3094,18 @@
       <c r="B7" s="13">
         <v>10</v>
       </c>
-      <c r="C7" s="88"/>
+      <c r="C7" s="57"/>
       <c r="D7" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E7" s="95"/>
-      <c r="F7" s="91" t="s">
+      <c r="E7" s="65"/>
+      <c r="F7" s="61" t="s">
         <v>90</v>
       </c>
-      <c r="G7" s="92"/>
-      <c r="H7" s="92"/>
-      <c r="I7" s="92"/>
-      <c r="J7" s="93"/>
+      <c r="G7" s="62"/>
+      <c r="H7" s="62"/>
+      <c r="I7" s="62"/>
+      <c r="J7" s="63"/>
       <c r="K7" s="13" t="s">
         <v>115</v>
       </c>
@@ -3112,18 +3117,18 @@
       <c r="B8" s="13">
         <v>11</v>
       </c>
-      <c r="C8" s="88"/>
+      <c r="C8" s="57"/>
       <c r="D8" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="E8" s="95"/>
-      <c r="F8" s="91">
+      <c r="E8" s="65"/>
+      <c r="F8" s="61">
         <v>102</v>
       </c>
-      <c r="G8" s="92"/>
-      <c r="H8" s="92"/>
-      <c r="I8" s="92"/>
-      <c r="J8" s="93"/>
+      <c r="G8" s="62"/>
+      <c r="H8" s="62"/>
+      <c r="I8" s="62"/>
+      <c r="J8" s="63"/>
       <c r="K8" s="13" t="s">
         <v>116</v>
       </c>
@@ -3135,18 +3140,18 @@
       <c r="B9" s="13">
         <v>12</v>
       </c>
-      <c r="C9" s="88"/>
+      <c r="C9" s="57"/>
       <c r="D9" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="E9" s="95"/>
-      <c r="F9" s="91" t="s">
+      <c r="E9" s="65"/>
+      <c r="F9" s="61" t="s">
         <v>93</v>
       </c>
-      <c r="G9" s="92"/>
-      <c r="H9" s="92"/>
-      <c r="I9" s="92"/>
-      <c r="J9" s="93"/>
+      <c r="G9" s="62"/>
+      <c r="H9" s="62"/>
+      <c r="I9" s="62"/>
+      <c r="J9" s="63"/>
       <c r="K9" s="13" t="s">
         <v>96</v>
       </c>
@@ -3158,18 +3163,18 @@
       <c r="B10" s="2">
         <v>13</v>
       </c>
-      <c r="C10" s="88"/>
+      <c r="C10" s="57"/>
       <c r="D10" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="E10" s="95"/>
-      <c r="F10" s="91" t="s">
+      <c r="E10" s="65"/>
+      <c r="F10" s="61" t="s">
         <v>100</v>
       </c>
-      <c r="G10" s="92"/>
-      <c r="H10" s="92"/>
-      <c r="I10" s="92"/>
-      <c r="J10" s="93"/>
+      <c r="G10" s="62"/>
+      <c r="H10" s="62"/>
+      <c r="I10" s="62"/>
+      <c r="J10" s="63"/>
       <c r="K10" s="2" t="s">
         <v>115</v>
       </c>
@@ -3181,18 +3186,18 @@
       <c r="B11" s="13">
         <v>14</v>
       </c>
-      <c r="C11" s="88"/>
+      <c r="C11" s="57"/>
       <c r="D11" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="E11" s="95"/>
-      <c r="F11" s="91" t="s">
+      <c r="E11" s="65"/>
+      <c r="F11" s="61" t="s">
         <v>96</v>
       </c>
-      <c r="G11" s="92"/>
-      <c r="H11" s="92"/>
-      <c r="I11" s="92"/>
-      <c r="J11" s="93"/>
+      <c r="G11" s="62"/>
+      <c r="H11" s="62"/>
+      <c r="I11" s="62"/>
+      <c r="J11" s="63"/>
       <c r="K11" s="13" t="s">
         <v>96</v>
       </c>
@@ -3204,20 +3209,20 @@
       <c r="B12" s="2">
         <v>15</v>
       </c>
-      <c r="C12" s="88"/>
+      <c r="C12" s="57"/>
       <c r="D12" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="E12" s="94" t="s">
+      <c r="E12" s="34" t="s">
         <v>114</v>
       </c>
-      <c r="F12" s="91" t="s">
+      <c r="F12" s="61" t="s">
         <v>85</v>
       </c>
-      <c r="G12" s="92"/>
-      <c r="H12" s="92"/>
-      <c r="I12" s="92"/>
-      <c r="J12" s="93"/>
+      <c r="G12" s="62"/>
+      <c r="H12" s="62"/>
+      <c r="I12" s="62"/>
+      <c r="J12" s="63"/>
       <c r="K12" s="2" t="s">
         <v>96</v>
       </c>
@@ -3233,83 +3238,83 @@
       <c r="K18" s="15"/>
     </row>
     <row r="19" spans="2:14" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="50" t="s">
+      <c r="B19" s="82" t="s">
         <v>57</v>
       </c>
-      <c r="C19" s="51"/>
-      <c r="D19" s="51"/>
-      <c r="E19" s="51"/>
-      <c r="F19" s="52" t="s">
+      <c r="C19" s="83"/>
+      <c r="D19" s="83"/>
+      <c r="E19" s="83"/>
+      <c r="F19" s="74" t="s">
         <v>58</v>
       </c>
-      <c r="G19" s="53"/>
-      <c r="H19" s="50" t="s">
+      <c r="G19" s="75"/>
+      <c r="H19" s="82" t="s">
         <v>59</v>
       </c>
-      <c r="I19" s="51"/>
-      <c r="J19" s="51"/>
-      <c r="K19" s="51"/>
-      <c r="L19" s="67"/>
-      <c r="M19" s="36" t="s">
+      <c r="I19" s="83"/>
+      <c r="J19" s="83"/>
+      <c r="K19" s="83"/>
+      <c r="L19" s="84"/>
+      <c r="M19" s="88" t="s">
         <v>60</v>
       </c>
-      <c r="N19" s="37"/>
+      <c r="N19" s="89"/>
     </row>
     <row r="20" spans="2:14" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="62" t="s">
+      <c r="B20" s="66" t="s">
         <v>35</v>
       </c>
-      <c r="C20" s="58" t="s">
+      <c r="C20" s="68" t="s">
         <v>36</v>
       </c>
-      <c r="D20" s="58" t="s">
+      <c r="D20" s="68" t="s">
         <v>37</v>
       </c>
-      <c r="E20" s="64" t="s">
+      <c r="E20" s="70" t="s">
         <v>61</v>
       </c>
-      <c r="F20" s="55" t="s">
+      <c r="F20" s="72" t="s">
         <v>62</v>
       </c>
-      <c r="G20" s="54" t="s">
+      <c r="G20" s="76" t="s">
         <v>63</v>
       </c>
-      <c r="H20" s="56" t="s">
+      <c r="H20" s="78" t="s">
         <v>64</v>
       </c>
-      <c r="I20" s="58" t="s">
+      <c r="I20" s="68" t="s">
         <v>35</v>
       </c>
-      <c r="J20" s="58" t="s">
+      <c r="J20" s="68" t="s">
         <v>36</v>
       </c>
-      <c r="K20" s="60" t="s">
+      <c r="K20" s="80" t="s">
         <v>38</v>
       </c>
-      <c r="L20" s="68" t="s">
+      <c r="L20" s="85" t="s">
         <v>65</v>
       </c>
-      <c r="M20" s="70" t="s">
+      <c r="M20" s="87" t="s">
         <v>66</v>
       </c>
-      <c r="N20" s="46" t="s">
+      <c r="N20" s="77" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B21" s="63"/>
-      <c r="C21" s="59"/>
-      <c r="D21" s="59"/>
-      <c r="E21" s="65"/>
-      <c r="F21" s="66"/>
-      <c r="G21" s="54"/>
-      <c r="H21" s="57"/>
-      <c r="I21" s="59"/>
-      <c r="J21" s="59"/>
-      <c r="K21" s="61"/>
-      <c r="L21" s="69"/>
-      <c r="M21" s="62"/>
-      <c r="N21" s="55"/>
+      <c r="B21" s="67"/>
+      <c r="C21" s="69"/>
+      <c r="D21" s="69"/>
+      <c r="E21" s="71"/>
+      <c r="F21" s="73"/>
+      <c r="G21" s="76"/>
+      <c r="H21" s="79"/>
+      <c r="I21" s="69"/>
+      <c r="J21" s="69"/>
+      <c r="K21" s="81"/>
+      <c r="L21" s="86"/>
+      <c r="M21" s="66"/>
+      <c r="N21" s="72"/>
     </row>
     <row r="22" spans="2:14" ht="144" x14ac:dyDescent="0.3">
       <c r="B22" s="17">
@@ -3321,10 +3326,10 @@
       <c r="D22" s="16">
         <v>2</v>
       </c>
-      <c r="E22" s="96">
+      <c r="E22" s="35">
         <v>1</v>
       </c>
-      <c r="F22" s="98" t="s">
+      <c r="F22" s="37" t="s">
         <v>119</v>
       </c>
       <c r="G22" s="8" t="s">
@@ -3343,7 +3348,7 @@
       <c r="K22" s="18">
         <v>0</v>
       </c>
-      <c r="L22" s="97">
+      <c r="L22" s="36">
         <v>1</v>
       </c>
       <c r="M22" s="6" t="s">
@@ -3355,21 +3360,14 @@
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="C6:C12"/>
-    <mergeCell ref="F5:J5"/>
-    <mergeCell ref="F6:J6"/>
-    <mergeCell ref="F7:J7"/>
-    <mergeCell ref="F8:J8"/>
-    <mergeCell ref="F9:J9"/>
-    <mergeCell ref="F10:J10"/>
-    <mergeCell ref="F11:J11"/>
-    <mergeCell ref="F12:J12"/>
-    <mergeCell ref="E6:E11"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="B3:L3"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="E4:J4"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
     <mergeCell ref="F19:G19"/>
     <mergeCell ref="G20:G21"/>
     <mergeCell ref="N20:N21"/>
@@ -3381,14 +3379,21 @@
     <mergeCell ref="L20:L21"/>
     <mergeCell ref="M20:M21"/>
     <mergeCell ref="M19:N19"/>
-    <mergeCell ref="D1:G1"/>
-    <mergeCell ref="B3:L3"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="E4:J4"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="C6:C12"/>
+    <mergeCell ref="F5:J5"/>
+    <mergeCell ref="F6:J6"/>
+    <mergeCell ref="F7:J7"/>
+    <mergeCell ref="F8:J8"/>
+    <mergeCell ref="F9:J9"/>
+    <mergeCell ref="F10:J10"/>
+    <mergeCell ref="F11:J11"/>
+    <mergeCell ref="F12:J12"/>
+    <mergeCell ref="E6:E11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3396,6 +3401,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010058284A30843C9F43BD758DDD8294D484" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="6d50638930d08c51b5585735b2be047e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fed1744a-f275-4023-9290-77fd546fd730" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4acb07121b76573bb3c966f3dcb1b903" ns2:_="">
     <xsd:import namespace="fed1744a-f275-4023-9290-77fd546fd730"/>
@@ -3539,22 +3559,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6597AB9C-DC10-4824-8900-518D3B18165A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5426D20B-58AE-4BE9-8733-DFB2BC19D8C6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{741A764F-DFF5-4AE4-B0E7-77BD148FABB8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3570,21 +3592,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5426D20B-58AE-4BE9-8733-DFB2BC19D8C6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6597AB9C-DC10-4824-8900-518D3B18165A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>